--- a/inst/resources/dependency_schema_data_household_template.xlsx
+++ b/inst/resources/dependency_schema_data_household_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\Positron\public_health_resources\inst\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SaeedRAHMAN\Documents\GitHub\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{117BE7C2-297A-469D-BB59-76FF72B535A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72A7868B-AD75-4B6F-8DAF-F8435B50BE8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="2325" windowWidth="24225" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -157,15 +157,9 @@
     <t>hh_size</t>
   </si>
   <si>
-    <t>num_hh &gt; 0</t>
-  </si>
-  <si>
     <t>flag_num_hh_outlier2</t>
   </si>
   <si>
-    <t>num_hh &lt; 20</t>
-  </si>
-  <si>
     <t>flag_warning</t>
   </si>
   <si>
@@ -2297,6 +2291,12 @@
   </si>
   <si>
     <t>fsl_lcsi_emergency_yes == 1 | fsl_lcsi_emergency_exhaust == 1 | fsl_lcsi_crisis_yes == 1 | fsl_lcsi_crisis_exhaust == 1</t>
+  </si>
+  <si>
+    <t>hh_size &gt; 0</t>
+  </si>
+  <si>
+    <t>hh_size &lt; 20</t>
   </si>
 </sst>
 </file>
@@ -3048,7 +3048,7 @@
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>44</v>
+        <v>756</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
@@ -3059,7 +3059,7 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
         <v>43</v>
@@ -3068,10 +3068,10 @@
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>46</v>
+        <v>757</v>
       </c>
       <c r="F13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -3079,16 +3079,16 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" t="s">
         <v>49</v>
       </c>
-      <c r="C14" t="s">
+      <c r="E14" t="s">
         <v>50</v>
-      </c>
-      <c r="D14" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" t="s">
-        <v>52</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
@@ -3099,16 +3099,16 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" t="s">
         <v>50</v>
-      </c>
-      <c r="D15" t="s">
-        <v>54</v>
-      </c>
-      <c r="E15" t="s">
-        <v>52</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
@@ -3119,16 +3119,16 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" t="s">
         <v>50</v>
-      </c>
-      <c r="D16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E16" t="s">
-        <v>52</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
@@ -3139,16 +3139,16 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" t="s">
         <v>50</v>
-      </c>
-      <c r="D17" t="s">
-        <v>58</v>
-      </c>
-      <c r="E17" t="s">
-        <v>52</v>
       </c>
       <c r="F17" t="s">
         <v>13</v>
@@ -3159,16 +3159,16 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D18" t="b">
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F18" t="s">
         <v>13</v>
@@ -3179,16 +3179,16 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" t="s">
         <v>61</v>
       </c>
-      <c r="C19" t="s">
+      <c r="E19" t="s">
         <v>62</v>
-      </c>
-      <c r="D19" t="s">
-        <v>63</v>
-      </c>
-      <c r="E19" t="s">
-        <v>64</v>
       </c>
       <c r="F19" t="s">
         <v>13</v>
@@ -3199,16 +3199,16 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" t="s">
         <v>65</v>
       </c>
-      <c r="C20" t="s">
+      <c r="E20" t="s">
         <v>66</v>
-      </c>
-      <c r="D20" t="s">
-        <v>67</v>
-      </c>
-      <c r="E20" t="s">
-        <v>68</v>
       </c>
       <c r="F20" t="s">
         <v>13</v>
@@ -3219,19 +3219,19 @@
         <v>8</v>
       </c>
       <c r="B21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" t="s">
         <v>69</v>
       </c>
-      <c r="C21" t="s">
-        <v>70</v>
-      </c>
-      <c r="D21" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" t="s">
-        <v>71</v>
-      </c>
       <c r="F21" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -3239,19 +3239,19 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D22" t="b">
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="F22" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -3259,19 +3259,19 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23" t="s">
         <v>74</v>
       </c>
-      <c r="C23" t="s">
+      <c r="E23" t="s">
         <v>75</v>
       </c>
-      <c r="D23" t="s">
-        <v>76</v>
-      </c>
-      <c r="E23" t="s">
-        <v>77</v>
-      </c>
       <c r="F23" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -3279,19 +3279,19 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" t="s">
         <v>78</v>
       </c>
-      <c r="C24" t="s">
-        <v>79</v>
-      </c>
-      <c r="D24" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" t="s">
-        <v>80</v>
-      </c>
       <c r="F24" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -3299,19 +3299,19 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" t="s">
+        <v>80</v>
+      </c>
+      <c r="D25" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" t="s">
         <v>81</v>
       </c>
-      <c r="C25" t="s">
-        <v>82</v>
-      </c>
-      <c r="D25" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" t="s">
-        <v>83</v>
-      </c>
       <c r="F25" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -3319,16 +3319,16 @@
         <v>8</v>
       </c>
       <c r="B26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" t="s">
         <v>84</v>
-      </c>
-      <c r="C26" t="s">
-        <v>85</v>
-      </c>
-      <c r="D26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" t="s">
-        <v>86</v>
       </c>
       <c r="F26" t="s">
         <v>13</v>
@@ -3339,16 +3339,16 @@
         <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D27" t="b">
         <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F27" t="s">
         <v>13</v>
@@ -3359,16 +3359,16 @@
         <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D28" t="b">
         <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F28" t="s">
         <v>13</v>
@@ -3379,16 +3379,16 @@
         <v>8</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D29" t="b">
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F29" t="s">
         <v>13</v>
@@ -3399,16 +3399,16 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" t="s">
+        <v>92</v>
+      </c>
+      <c r="D30" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" t="s">
         <v>93</v>
-      </c>
-      <c r="C30" t="s">
-        <v>94</v>
-      </c>
-      <c r="D30" t="b">
-        <v>1</v>
-      </c>
-      <c r="E30" t="s">
-        <v>95</v>
       </c>
       <c r="F30" t="s">
         <v>13</v>
@@ -3419,16 +3419,16 @@
         <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D31" t="b">
         <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F31" t="s">
         <v>13</v>
@@ -3439,16 +3439,16 @@
         <v>8</v>
       </c>
       <c r="B32" t="s">
+        <v>96</v>
+      </c>
+      <c r="C32" t="s">
+        <v>97</v>
+      </c>
+      <c r="D32" t="s">
         <v>98</v>
       </c>
-      <c r="C32" t="s">
+      <c r="E32" t="s">
         <v>99</v>
-      </c>
-      <c r="D32" t="s">
-        <v>100</v>
-      </c>
-      <c r="E32" t="s">
-        <v>101</v>
       </c>
       <c r="F32" t="s">
         <v>13</v>
@@ -3459,16 +3459,16 @@
         <v>8</v>
       </c>
       <c r="B33" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33" t="s">
+        <v>101</v>
+      </c>
+      <c r="D33" t="s">
         <v>102</v>
       </c>
-      <c r="C33" t="s">
+      <c r="E33" t="s">
         <v>103</v>
-      </c>
-      <c r="D33" t="s">
-        <v>104</v>
-      </c>
-      <c r="E33" t="s">
-        <v>105</v>
       </c>
       <c r="F33" t="s">
         <v>13</v>
@@ -3479,16 +3479,16 @@
         <v>8</v>
       </c>
       <c r="B34" t="s">
+        <v>104</v>
+      </c>
+      <c r="C34" t="s">
+        <v>105</v>
+      </c>
+      <c r="D34" t="s">
         <v>106</v>
       </c>
-      <c r="C34" t="s">
+      <c r="E34" t="s">
         <v>107</v>
-      </c>
-      <c r="D34" t="s">
-        <v>108</v>
-      </c>
-      <c r="E34" t="s">
-        <v>109</v>
       </c>
       <c r="F34" t="s">
         <v>13</v>
@@ -3499,16 +3499,16 @@
         <v>8</v>
       </c>
       <c r="B35" t="s">
+        <v>108</v>
+      </c>
+      <c r="C35" t="s">
+        <v>109</v>
+      </c>
+      <c r="D35" t="s">
         <v>110</v>
       </c>
-      <c r="C35" t="s">
+      <c r="E35" t="s">
         <v>111</v>
-      </c>
-      <c r="D35" t="s">
-        <v>112</v>
-      </c>
-      <c r="E35" t="s">
-        <v>113</v>
       </c>
       <c r="F35" t="s">
         <v>13</v>
@@ -3519,16 +3519,16 @@
         <v>8</v>
       </c>
       <c r="B36" t="s">
+        <v>112</v>
+      </c>
+      <c r="C36" t="s">
+        <v>113</v>
+      </c>
+      <c r="D36" t="s">
         <v>114</v>
       </c>
-      <c r="C36" t="s">
+      <c r="E36" t="s">
         <v>115</v>
-      </c>
-      <c r="D36" t="s">
-        <v>116</v>
-      </c>
-      <c r="E36" t="s">
-        <v>117</v>
       </c>
       <c r="F36" t="s">
         <v>13</v>
@@ -3539,16 +3539,16 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
+        <v>116</v>
+      </c>
+      <c r="C37" t="s">
+        <v>117</v>
+      </c>
+      <c r="D37" t="s">
         <v>118</v>
       </c>
-      <c r="C37" t="s">
+      <c r="E37" t="s">
         <v>119</v>
-      </c>
-      <c r="D37" t="s">
-        <v>120</v>
-      </c>
-      <c r="E37" t="s">
-        <v>121</v>
       </c>
       <c r="F37" t="s">
         <v>13</v>
@@ -3559,16 +3559,16 @@
         <v>8</v>
       </c>
       <c r="B38" t="s">
+        <v>120</v>
+      </c>
+      <c r="C38" t="s">
+        <v>121</v>
+      </c>
+      <c r="D38" t="s">
         <v>122</v>
       </c>
-      <c r="C38" t="s">
+      <c r="E38" t="s">
         <v>123</v>
-      </c>
-      <c r="D38" t="s">
-        <v>124</v>
-      </c>
-      <c r="E38" t="s">
-        <v>125</v>
       </c>
       <c r="F38" t="s">
         <v>13</v>
@@ -3579,16 +3579,16 @@
         <v>8</v>
       </c>
       <c r="B39" t="s">
+        <v>124</v>
+      </c>
+      <c r="C39" t="s">
+        <v>125</v>
+      </c>
+      <c r="D39" t="s">
         <v>126</v>
       </c>
-      <c r="C39" t="s">
+      <c r="E39" t="s">
         <v>127</v>
-      </c>
-      <c r="D39" t="s">
-        <v>128</v>
-      </c>
-      <c r="E39" t="s">
-        <v>129</v>
       </c>
       <c r="F39" t="s">
         <v>13</v>
@@ -3599,16 +3599,16 @@
         <v>8</v>
       </c>
       <c r="B40" t="s">
+        <v>128</v>
+      </c>
+      <c r="C40" t="s">
+        <v>129</v>
+      </c>
+      <c r="D40" t="s">
         <v>130</v>
       </c>
-      <c r="C40" t="s">
+      <c r="E40" t="s">
         <v>131</v>
-      </c>
-      <c r="D40" t="s">
-        <v>132</v>
-      </c>
-      <c r="E40" t="s">
-        <v>133</v>
       </c>
       <c r="F40" t="s">
         <v>13</v>
@@ -3619,16 +3619,16 @@
         <v>8</v>
       </c>
       <c r="B41" t="s">
+        <v>132</v>
+      </c>
+      <c r="C41" t="s">
+        <v>97</v>
+      </c>
+      <c r="D41" t="s">
+        <v>133</v>
+      </c>
+      <c r="E41" t="s">
         <v>134</v>
-      </c>
-      <c r="C41" t="s">
-        <v>99</v>
-      </c>
-      <c r="D41" t="s">
-        <v>135</v>
-      </c>
-      <c r="E41" t="s">
-        <v>136</v>
       </c>
       <c r="F41" t="s">
         <v>13</v>
@@ -3639,16 +3639,16 @@
         <v>8</v>
       </c>
       <c r="B42" t="s">
+        <v>135</v>
+      </c>
+      <c r="C42" t="s">
+        <v>101</v>
+      </c>
+      <c r="D42" t="s">
+        <v>136</v>
+      </c>
+      <c r="E42" t="s">
         <v>137</v>
-      </c>
-      <c r="C42" t="s">
-        <v>103</v>
-      </c>
-      <c r="D42" t="s">
-        <v>138</v>
-      </c>
-      <c r="E42" t="s">
-        <v>139</v>
       </c>
       <c r="F42" t="s">
         <v>13</v>
@@ -3659,16 +3659,16 @@
         <v>8</v>
       </c>
       <c r="B43" t="s">
+        <v>138</v>
+      </c>
+      <c r="C43" t="s">
+        <v>105</v>
+      </c>
+      <c r="D43" t="s">
+        <v>139</v>
+      </c>
+      <c r="E43" t="s">
         <v>140</v>
-      </c>
-      <c r="C43" t="s">
-        <v>107</v>
-      </c>
-      <c r="D43" t="s">
-        <v>141</v>
-      </c>
-      <c r="E43" t="s">
-        <v>142</v>
       </c>
       <c r="F43" t="s">
         <v>13</v>
@@ -3679,16 +3679,16 @@
         <v>8</v>
       </c>
       <c r="B44" t="s">
+        <v>141</v>
+      </c>
+      <c r="C44" t="s">
+        <v>109</v>
+      </c>
+      <c r="D44" t="s">
+        <v>142</v>
+      </c>
+      <c r="E44" t="s">
         <v>143</v>
-      </c>
-      <c r="C44" t="s">
-        <v>111</v>
-      </c>
-      <c r="D44" t="s">
-        <v>144</v>
-      </c>
-      <c r="E44" t="s">
-        <v>145</v>
       </c>
       <c r="F44" t="s">
         <v>13</v>
@@ -3699,16 +3699,16 @@
         <v>8</v>
       </c>
       <c r="B45" t="s">
+        <v>144</v>
+      </c>
+      <c r="C45" t="s">
+        <v>113</v>
+      </c>
+      <c r="D45" t="s">
+        <v>145</v>
+      </c>
+      <c r="E45" t="s">
         <v>146</v>
-      </c>
-      <c r="C45" t="s">
-        <v>115</v>
-      </c>
-      <c r="D45" t="s">
-        <v>147</v>
-      </c>
-      <c r="E45" t="s">
-        <v>148</v>
       </c>
       <c r="F45" t="s">
         <v>13</v>
@@ -3719,16 +3719,16 @@
         <v>8</v>
       </c>
       <c r="B46" t="s">
+        <v>147</v>
+      </c>
+      <c r="C46" t="s">
+        <v>117</v>
+      </c>
+      <c r="D46" t="s">
+        <v>148</v>
+      </c>
+      <c r="E46" t="s">
         <v>149</v>
-      </c>
-      <c r="C46" t="s">
-        <v>119</v>
-      </c>
-      <c r="D46" t="s">
-        <v>150</v>
-      </c>
-      <c r="E46" t="s">
-        <v>151</v>
       </c>
       <c r="F46" t="s">
         <v>13</v>
@@ -3739,16 +3739,16 @@
         <v>8</v>
       </c>
       <c r="B47" t="s">
+        <v>150</v>
+      </c>
+      <c r="C47" t="s">
+        <v>121</v>
+      </c>
+      <c r="D47" t="s">
+        <v>151</v>
+      </c>
+      <c r="E47" t="s">
         <v>152</v>
-      </c>
-      <c r="C47" t="s">
-        <v>123</v>
-      </c>
-      <c r="D47" t="s">
-        <v>153</v>
-      </c>
-      <c r="E47" t="s">
-        <v>154</v>
       </c>
       <c r="F47" t="s">
         <v>13</v>
@@ -3759,16 +3759,16 @@
         <v>8</v>
       </c>
       <c r="B48" t="s">
+        <v>153</v>
+      </c>
+      <c r="C48" t="s">
+        <v>125</v>
+      </c>
+      <c r="D48" t="s">
+        <v>154</v>
+      </c>
+      <c r="E48" t="s">
         <v>155</v>
-      </c>
-      <c r="C48" t="s">
-        <v>127</v>
-      </c>
-      <c r="D48" t="s">
-        <v>156</v>
-      </c>
-      <c r="E48" t="s">
-        <v>157</v>
       </c>
       <c r="F48" t="s">
         <v>13</v>
@@ -3779,16 +3779,16 @@
         <v>8</v>
       </c>
       <c r="B49" t="s">
+        <v>156</v>
+      </c>
+      <c r="C49" t="s">
+        <v>129</v>
+      </c>
+      <c r="D49" t="s">
+        <v>157</v>
+      </c>
+      <c r="E49" t="s">
         <v>158</v>
-      </c>
-      <c r="C49" t="s">
-        <v>131</v>
-      </c>
-      <c r="D49" t="s">
-        <v>159</v>
-      </c>
-      <c r="E49" t="s">
-        <v>160</v>
       </c>
       <c r="F49" t="s">
         <v>13</v>
@@ -3799,19 +3799,19 @@
         <v>8</v>
       </c>
       <c r="B50" t="s">
+        <v>159</v>
+      </c>
+      <c r="C50" t="s">
+        <v>160</v>
+      </c>
+      <c r="D50" t="s">
         <v>161</v>
       </c>
-      <c r="C50" t="s">
+      <c r="E50" t="s">
         <v>162</v>
       </c>
-      <c r="D50" t="s">
-        <v>163</v>
-      </c>
-      <c r="E50" t="s">
-        <v>164</v>
-      </c>
       <c r="F50" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -3819,19 +3819,19 @@
         <v>8</v>
       </c>
       <c r="B51" t="s">
+        <v>163</v>
+      </c>
+      <c r="C51" t="s">
+        <v>164</v>
+      </c>
+      <c r="D51" t="b">
+        <v>1</v>
+      </c>
+      <c r="E51" t="s">
         <v>165</v>
       </c>
-      <c r="C51" t="s">
-        <v>166</v>
-      </c>
-      <c r="D51" t="b">
-        <v>1</v>
-      </c>
-      <c r="E51" t="s">
-        <v>167</v>
-      </c>
       <c r="F51" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -3839,19 +3839,19 @@
         <v>8</v>
       </c>
       <c r="B52" t="s">
+        <v>166</v>
+      </c>
+      <c r="C52" t="s">
+        <v>167</v>
+      </c>
+      <c r="D52" t="s">
         <v>168</v>
       </c>
-      <c r="C52" t="s">
+      <c r="E52" t="s">
         <v>169</v>
       </c>
-      <c r="D52" t="s">
-        <v>170</v>
-      </c>
-      <c r="E52" t="s">
-        <v>171</v>
-      </c>
       <c r="F52" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -3859,16 +3859,16 @@
         <v>8</v>
       </c>
       <c r="B53" t="s">
+        <v>170</v>
+      </c>
+      <c r="C53" t="s">
+        <v>171</v>
+      </c>
+      <c r="D53" t="b">
+        <v>1</v>
+      </c>
+      <c r="E53" t="s">
         <v>172</v>
-      </c>
-      <c r="C53" t="s">
-        <v>173</v>
-      </c>
-      <c r="D53" t="b">
-        <v>1</v>
-      </c>
-      <c r="E53" t="s">
-        <v>174</v>
       </c>
       <c r="F53" t="s">
         <v>13</v>
@@ -3879,16 +3879,16 @@
         <v>8</v>
       </c>
       <c r="B54" t="s">
+        <v>173</v>
+      </c>
+      <c r="C54" t="s">
+        <v>174</v>
+      </c>
+      <c r="D54" t="s">
         <v>175</v>
       </c>
-      <c r="C54" t="s">
+      <c r="E54" t="s">
         <v>176</v>
-      </c>
-      <c r="D54" t="s">
-        <v>177</v>
-      </c>
-      <c r="E54" t="s">
-        <v>178</v>
       </c>
       <c r="F54" t="s">
         <v>13</v>
@@ -3899,19 +3899,19 @@
         <v>8</v>
       </c>
       <c r="B55" t="s">
+        <v>177</v>
+      </c>
+      <c r="C55" t="s">
+        <v>178</v>
+      </c>
+      <c r="D55" t="b">
+        <v>1</v>
+      </c>
+      <c r="E55" t="s">
         <v>179</v>
       </c>
-      <c r="C55" t="s">
-        <v>180</v>
-      </c>
-      <c r="D55" t="b">
-        <v>1</v>
-      </c>
-      <c r="E55" t="s">
-        <v>181</v>
-      </c>
       <c r="F55" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3919,16 +3919,16 @@
         <v>8</v>
       </c>
       <c r="B56" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C56" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D56" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="E56" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="F56" t="s">
         <v>13</v>
@@ -3939,19 +3939,19 @@
         <v>8</v>
       </c>
       <c r="B57" t="s">
+        <v>182</v>
+      </c>
+      <c r="C57" t="s">
+        <v>183</v>
+      </c>
+      <c r="D57" t="b">
+        <v>1</v>
+      </c>
+      <c r="E57" t="s">
         <v>184</v>
       </c>
-      <c r="C57" t="s">
-        <v>185</v>
-      </c>
-      <c r="D57" t="b">
-        <v>1</v>
-      </c>
-      <c r="E57" t="s">
-        <v>186</v>
-      </c>
       <c r="F57" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -3959,16 +3959,16 @@
         <v>8</v>
       </c>
       <c r="B58" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C58" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="D58" t="b">
         <v>1</v>
       </c>
       <c r="E58" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F58" t="s">
         <v>13</v>
@@ -3979,16 +3979,16 @@
         <v>8</v>
       </c>
       <c r="B59" t="s">
+        <v>187</v>
+      </c>
+      <c r="C59" t="s">
+        <v>188</v>
+      </c>
+      <c r="D59" t="b">
+        <v>1</v>
+      </c>
+      <c r="E59" t="s">
         <v>189</v>
-      </c>
-      <c r="C59" t="s">
-        <v>190</v>
-      </c>
-      <c r="D59" t="b">
-        <v>1</v>
-      </c>
-      <c r="E59" t="s">
-        <v>191</v>
       </c>
       <c r="F59" t="s">
         <v>13</v>
@@ -3999,16 +3999,16 @@
         <v>8</v>
       </c>
       <c r="B60" t="s">
+        <v>190</v>
+      </c>
+      <c r="C60" t="s">
+        <v>191</v>
+      </c>
+      <c r="D60" t="s">
         <v>192</v>
       </c>
-      <c r="C60" t="s">
+      <c r="E60" t="s">
         <v>193</v>
-      </c>
-      <c r="D60" t="s">
-        <v>194</v>
-      </c>
-      <c r="E60" t="s">
-        <v>195</v>
       </c>
       <c r="F60" t="s">
         <v>13</v>
@@ -4019,16 +4019,16 @@
         <v>8</v>
       </c>
       <c r="B61" t="s">
+        <v>194</v>
+      </c>
+      <c r="C61" t="s">
+        <v>191</v>
+      </c>
+      <c r="D61" t="s">
+        <v>195</v>
+      </c>
+      <c r="E61" t="s">
         <v>196</v>
-      </c>
-      <c r="C61" t="s">
-        <v>193</v>
-      </c>
-      <c r="D61" t="s">
-        <v>197</v>
-      </c>
-      <c r="E61" t="s">
-        <v>198</v>
       </c>
       <c r="F61" t="s">
         <v>13</v>
@@ -4039,16 +4039,16 @@
         <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C62" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D62" t="b">
         <v>1</v>
       </c>
       <c r="E62" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F62" t="s">
         <v>13</v>
@@ -4059,16 +4059,16 @@
         <v>8</v>
       </c>
       <c r="B63" t="s">
+        <v>199</v>
+      </c>
+      <c r="C63" t="s">
+        <v>200</v>
+      </c>
+      <c r="D63" t="b">
+        <v>1</v>
+      </c>
+      <c r="E63" t="s">
         <v>201</v>
-      </c>
-      <c r="C63" t="s">
-        <v>202</v>
-      </c>
-      <c r="D63" t="b">
-        <v>1</v>
-      </c>
-      <c r="E63" t="s">
-        <v>203</v>
       </c>
       <c r="F63" t="s">
         <v>13</v>
@@ -4079,16 +4079,16 @@
         <v>8</v>
       </c>
       <c r="B64" t="s">
+        <v>202</v>
+      </c>
+      <c r="C64" t="s">
+        <v>203</v>
+      </c>
+      <c r="D64" t="b">
+        <v>1</v>
+      </c>
+      <c r="E64" t="s">
         <v>204</v>
-      </c>
-      <c r="C64" t="s">
-        <v>205</v>
-      </c>
-      <c r="D64" t="b">
-        <v>1</v>
-      </c>
-      <c r="E64" t="s">
-        <v>206</v>
       </c>
       <c r="F64" t="s">
         <v>13</v>
@@ -4099,16 +4099,16 @@
         <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C65" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D65" t="b">
         <v>1</v>
       </c>
       <c r="E65" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F65" t="s">
         <v>13</v>
@@ -4119,16 +4119,16 @@
         <v>8</v>
       </c>
       <c r="B66" t="s">
+        <v>207</v>
+      </c>
+      <c r="C66" t="s">
+        <v>208</v>
+      </c>
+      <c r="D66" t="b">
+        <v>1</v>
+      </c>
+      <c r="E66" t="s">
         <v>209</v>
-      </c>
-      <c r="C66" t="s">
-        <v>210</v>
-      </c>
-      <c r="D66" t="b">
-        <v>1</v>
-      </c>
-      <c r="E66" t="s">
-        <v>211</v>
       </c>
       <c r="F66" t="s">
         <v>13</v>
@@ -4139,16 +4139,16 @@
         <v>8</v>
       </c>
       <c r="B67" t="s">
+        <v>210</v>
+      </c>
+      <c r="C67" t="s">
+        <v>211</v>
+      </c>
+      <c r="D67" t="b">
+        <v>1</v>
+      </c>
+      <c r="E67" t="s">
         <v>212</v>
-      </c>
-      <c r="C67" t="s">
-        <v>213</v>
-      </c>
-      <c r="D67" t="b">
-        <v>1</v>
-      </c>
-      <c r="E67" t="s">
-        <v>214</v>
       </c>
       <c r="F67" t="s">
         <v>13</v>
@@ -4159,16 +4159,16 @@
         <v>8</v>
       </c>
       <c r="B68" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C68" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D68" t="b">
         <v>1</v>
       </c>
       <c r="E68" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F68" t="s">
         <v>13</v>
@@ -4179,16 +4179,16 @@
         <v>8</v>
       </c>
       <c r="B69" t="s">
+        <v>215</v>
+      </c>
+      <c r="C69" t="s">
+        <v>216</v>
+      </c>
+      <c r="D69" t="b">
+        <v>1</v>
+      </c>
+      <c r="E69" t="s">
         <v>217</v>
-      </c>
-      <c r="C69" t="s">
-        <v>218</v>
-      </c>
-      <c r="D69" t="b">
-        <v>1</v>
-      </c>
-      <c r="E69" t="s">
-        <v>219</v>
       </c>
       <c r="F69" t="s">
         <v>13</v>
@@ -4199,16 +4199,16 @@
         <v>8</v>
       </c>
       <c r="B70" t="s">
+        <v>218</v>
+      </c>
+      <c r="C70" t="s">
+        <v>219</v>
+      </c>
+      <c r="D70" t="b">
+        <v>1</v>
+      </c>
+      <c r="E70" t="s">
         <v>220</v>
-      </c>
-      <c r="C70" t="s">
-        <v>221</v>
-      </c>
-      <c r="D70" t="b">
-        <v>1</v>
-      </c>
-      <c r="E70" t="s">
-        <v>222</v>
       </c>
       <c r="F70" t="s">
         <v>13</v>
@@ -4219,16 +4219,16 @@
         <v>8</v>
       </c>
       <c r="B71" t="s">
+        <v>221</v>
+      </c>
+      <c r="C71" t="s">
+        <v>222</v>
+      </c>
+      <c r="D71" t="b">
+        <v>1</v>
+      </c>
+      <c r="E71" t="s">
         <v>223</v>
-      </c>
-      <c r="C71" t="s">
-        <v>224</v>
-      </c>
-      <c r="D71" t="b">
-        <v>1</v>
-      </c>
-      <c r="E71" t="s">
-        <v>225</v>
       </c>
       <c r="F71" t="s">
         <v>13</v>
@@ -4239,16 +4239,16 @@
         <v>8</v>
       </c>
       <c r="B72" t="s">
+        <v>224</v>
+      </c>
+      <c r="C72" t="s">
+        <v>225</v>
+      </c>
+      <c r="D72" t="b">
+        <v>1</v>
+      </c>
+      <c r="E72" t="s">
         <v>226</v>
-      </c>
-      <c r="C72" t="s">
-        <v>227</v>
-      </c>
-      <c r="D72" t="b">
-        <v>1</v>
-      </c>
-      <c r="E72" t="s">
-        <v>228</v>
       </c>
       <c r="F72" t="s">
         <v>13</v>
@@ -4259,16 +4259,16 @@
         <v>8</v>
       </c>
       <c r="B73" t="s">
+        <v>227</v>
+      </c>
+      <c r="C73" t="s">
+        <v>228</v>
+      </c>
+      <c r="D73" t="b">
+        <v>1</v>
+      </c>
+      <c r="E73" t="s">
         <v>229</v>
-      </c>
-      <c r="C73" t="s">
-        <v>230</v>
-      </c>
-      <c r="D73" t="b">
-        <v>1</v>
-      </c>
-      <c r="E73" t="s">
-        <v>231</v>
       </c>
       <c r="F73" t="s">
         <v>13</v>
@@ -4279,16 +4279,16 @@
         <v>8</v>
       </c>
       <c r="B74" t="s">
+        <v>230</v>
+      </c>
+      <c r="C74" t="s">
+        <v>231</v>
+      </c>
+      <c r="D74" t="b">
+        <v>1</v>
+      </c>
+      <c r="E74" t="s">
         <v>232</v>
-      </c>
-      <c r="C74" t="s">
-        <v>233</v>
-      </c>
-      <c r="D74" t="b">
-        <v>1</v>
-      </c>
-      <c r="E74" t="s">
-        <v>234</v>
       </c>
       <c r="F74" t="s">
         <v>13</v>
@@ -4299,16 +4299,16 @@
         <v>8</v>
       </c>
       <c r="B75" t="s">
+        <v>233</v>
+      </c>
+      <c r="C75" t="s">
+        <v>234</v>
+      </c>
+      <c r="D75" t="b">
+        <v>1</v>
+      </c>
+      <c r="E75" t="s">
         <v>235</v>
-      </c>
-      <c r="C75" t="s">
-        <v>236</v>
-      </c>
-      <c r="D75" t="b">
-        <v>1</v>
-      </c>
-      <c r="E75" t="s">
-        <v>237</v>
       </c>
       <c r="F75" t="s">
         <v>13</v>
@@ -4319,19 +4319,19 @@
         <v>8</v>
       </c>
       <c r="B76" t="s">
+        <v>236</v>
+      </c>
+      <c r="C76" t="s">
+        <v>174</v>
+      </c>
+      <c r="D76" t="s">
+        <v>237</v>
+      </c>
+      <c r="E76" t="s">
         <v>238</v>
       </c>
-      <c r="C76" t="s">
-        <v>176</v>
-      </c>
-      <c r="D76" t="s">
-        <v>239</v>
-      </c>
-      <c r="E76" t="s">
-        <v>240</v>
-      </c>
       <c r="F76" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -4339,16 +4339,16 @@
         <v>8</v>
       </c>
       <c r="B77" t="s">
+        <v>240</v>
+      </c>
+      <c r="C77" t="s">
+        <v>241</v>
+      </c>
+      <c r="D77" t="s">
         <v>242</v>
       </c>
-      <c r="C77" t="s">
+      <c r="E77" t="s">
         <v>243</v>
-      </c>
-      <c r="D77" t="s">
-        <v>244</v>
-      </c>
-      <c r="E77" t="s">
-        <v>245</v>
       </c>
       <c r="F77" t="s">
         <v>13</v>
@@ -4359,16 +4359,16 @@
         <v>8</v>
       </c>
       <c r="B78" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C78" t="s">
+        <v>241</v>
+      </c>
+      <c r="D78" t="s">
+        <v>245</v>
+      </c>
+      <c r="E78" t="s">
         <v>243</v>
-      </c>
-      <c r="D78" t="s">
-        <v>247</v>
-      </c>
-      <c r="E78" t="s">
-        <v>245</v>
       </c>
       <c r="F78" t="s">
         <v>13</v>
@@ -4379,16 +4379,16 @@
         <v>8</v>
       </c>
       <c r="B79" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C79" t="s">
+        <v>241</v>
+      </c>
+      <c r="D79" t="s">
+        <v>247</v>
+      </c>
+      <c r="E79" t="s">
         <v>243</v>
-      </c>
-      <c r="D79" t="s">
-        <v>249</v>
-      </c>
-      <c r="E79" t="s">
-        <v>245</v>
       </c>
       <c r="F79" t="s">
         <v>13</v>
@@ -4399,16 +4399,16 @@
         <v>8</v>
       </c>
       <c r="B80" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C80" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D80" t="b">
         <v>1</v>
       </c>
       <c r="E80" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F80" t="s">
         <v>13</v>
@@ -4419,16 +4419,16 @@
         <v>8</v>
       </c>
       <c r="B81" t="s">
+        <v>250</v>
+      </c>
+      <c r="C81" t="s">
+        <v>251</v>
+      </c>
+      <c r="D81" t="b">
+        <v>1</v>
+      </c>
+      <c r="E81" t="s">
         <v>252</v>
-      </c>
-      <c r="C81" t="s">
-        <v>253</v>
-      </c>
-      <c r="D81" t="b">
-        <v>1</v>
-      </c>
-      <c r="E81" t="s">
-        <v>254</v>
       </c>
       <c r="F81" t="s">
         <v>13</v>
@@ -4439,16 +4439,16 @@
         <v>8</v>
       </c>
       <c r="B82" t="s">
+        <v>253</v>
+      </c>
+      <c r="C82" t="s">
+        <v>254</v>
+      </c>
+      <c r="D82" t="b">
+        <v>1</v>
+      </c>
+      <c r="E82" t="s">
         <v>255</v>
-      </c>
-      <c r="C82" t="s">
-        <v>256</v>
-      </c>
-      <c r="D82" t="b">
-        <v>1</v>
-      </c>
-      <c r="E82" t="s">
-        <v>257</v>
       </c>
       <c r="F82" t="s">
         <v>13</v>
@@ -4459,16 +4459,16 @@
         <v>8</v>
       </c>
       <c r="B83" t="s">
+        <v>256</v>
+      </c>
+      <c r="C83" t="s">
+        <v>257</v>
+      </c>
+      <c r="D83" t="s">
         <v>258</v>
       </c>
-      <c r="C83" t="s">
+      <c r="E83" t="s">
         <v>259</v>
-      </c>
-      <c r="D83" t="s">
-        <v>260</v>
-      </c>
-      <c r="E83" t="s">
-        <v>261</v>
       </c>
       <c r="F83" t="s">
         <v>13</v>
@@ -4479,16 +4479,16 @@
         <v>8</v>
       </c>
       <c r="B84" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C84" t="s">
+        <v>257</v>
+      </c>
+      <c r="D84" t="s">
+        <v>261</v>
+      </c>
+      <c r="E84" t="s">
         <v>259</v>
-      </c>
-      <c r="D84" t="s">
-        <v>263</v>
-      </c>
-      <c r="E84" t="s">
-        <v>261</v>
       </c>
       <c r="F84" t="s">
         <v>13</v>
@@ -4499,16 +4499,16 @@
         <v>8</v>
       </c>
       <c r="B85" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C85" t="s">
+        <v>257</v>
+      </c>
+      <c r="D85" t="s">
+        <v>263</v>
+      </c>
+      <c r="E85" t="s">
         <v>259</v>
-      </c>
-      <c r="D85" t="s">
-        <v>265</v>
-      </c>
-      <c r="E85" t="s">
-        <v>261</v>
       </c>
       <c r="F85" t="s">
         <v>13</v>
@@ -4519,16 +4519,16 @@
         <v>8</v>
       </c>
       <c r="B86" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D86" t="b">
         <v>1</v>
       </c>
       <c r="E86" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F86" t="s">
         <v>13</v>
@@ -4539,16 +4539,16 @@
         <v>8</v>
       </c>
       <c r="B87" t="s">
+        <v>266</v>
+      </c>
+      <c r="C87" t="s">
+        <v>267</v>
+      </c>
+      <c r="D87" t="b">
+        <v>1</v>
+      </c>
+      <c r="E87" t="s">
         <v>268</v>
-      </c>
-      <c r="C87" t="s">
-        <v>269</v>
-      </c>
-      <c r="D87" t="b">
-        <v>1</v>
-      </c>
-      <c r="E87" t="s">
-        <v>270</v>
       </c>
       <c r="F87" t="s">
         <v>13</v>
@@ -4559,16 +4559,16 @@
         <v>8</v>
       </c>
       <c r="B88" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C88" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D88" t="b">
         <v>1</v>
       </c>
       <c r="E88" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F88" t="s">
         <v>13</v>
@@ -4579,16 +4579,16 @@
         <v>8</v>
       </c>
       <c r="B89" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C89" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D89" t="b">
         <v>1</v>
       </c>
       <c r="E89" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F89" t="s">
         <v>13</v>
@@ -4599,16 +4599,16 @@
         <v>8</v>
       </c>
       <c r="B90" t="s">
+        <v>273</v>
+      </c>
+      <c r="C90" t="s">
+        <v>274</v>
+      </c>
+      <c r="D90" t="b">
+        <v>1</v>
+      </c>
+      <c r="E90" t="s">
         <v>275</v>
-      </c>
-      <c r="C90" t="s">
-        <v>276</v>
-      </c>
-      <c r="D90" t="b">
-        <v>1</v>
-      </c>
-      <c r="E90" t="s">
-        <v>277</v>
       </c>
       <c r="F90" t="s">
         <v>13</v>
@@ -4619,16 +4619,16 @@
         <v>8</v>
       </c>
       <c r="B91" t="s">
+        <v>276</v>
+      </c>
+      <c r="C91" t="s">
+        <v>277</v>
+      </c>
+      <c r="D91" t="b">
+        <v>1</v>
+      </c>
+      <c r="E91" t="s">
         <v>278</v>
-      </c>
-      <c r="C91" t="s">
-        <v>279</v>
-      </c>
-      <c r="D91" t="b">
-        <v>1</v>
-      </c>
-      <c r="E91" t="s">
-        <v>280</v>
       </c>
       <c r="F91" t="s">
         <v>13</v>
@@ -4639,16 +4639,16 @@
         <v>8</v>
       </c>
       <c r="B92" t="s">
+        <v>279</v>
+      </c>
+      <c r="C92" t="s">
+        <v>280</v>
+      </c>
+      <c r="D92" t="s">
         <v>281</v>
       </c>
-      <c r="C92" t="s">
+      <c r="E92" t="s">
         <v>282</v>
-      </c>
-      <c r="D92" t="s">
-        <v>283</v>
-      </c>
-      <c r="E92" t="s">
-        <v>284</v>
       </c>
       <c r="F92" t="s">
         <v>13</v>
@@ -4659,16 +4659,16 @@
         <v>8</v>
       </c>
       <c r="B93" t="s">
+        <v>283</v>
+      </c>
+      <c r="C93" t="s">
+        <v>284</v>
+      </c>
+      <c r="D93" t="s">
         <v>285</v>
       </c>
-      <c r="C93" t="s">
+      <c r="E93" t="s">
         <v>286</v>
-      </c>
-      <c r="D93" t="s">
-        <v>287</v>
-      </c>
-      <c r="E93" t="s">
-        <v>288</v>
       </c>
       <c r="F93" t="s">
         <v>13</v>
@@ -4679,16 +4679,16 @@
         <v>8</v>
       </c>
       <c r="B94" t="s">
+        <v>287</v>
+      </c>
+      <c r="C94" t="s">
+        <v>288</v>
+      </c>
+      <c r="D94" t="s">
         <v>289</v>
       </c>
-      <c r="C94" t="s">
+      <c r="E94" t="s">
         <v>290</v>
-      </c>
-      <c r="D94" t="s">
-        <v>291</v>
-      </c>
-      <c r="E94" t="s">
-        <v>292</v>
       </c>
       <c r="F94" t="s">
         <v>13</v>
@@ -4699,16 +4699,16 @@
         <v>8</v>
       </c>
       <c r="B95" t="s">
+        <v>291</v>
+      </c>
+      <c r="C95" t="s">
+        <v>292</v>
+      </c>
+      <c r="D95" t="s">
         <v>293</v>
       </c>
-      <c r="C95" t="s">
+      <c r="E95" t="s">
         <v>294</v>
-      </c>
-      <c r="D95" t="s">
-        <v>295</v>
-      </c>
-      <c r="E95" t="s">
-        <v>296</v>
       </c>
       <c r="F95" t="s">
         <v>13</v>
@@ -4719,16 +4719,16 @@
         <v>8</v>
       </c>
       <c r="B96" t="s">
+        <v>295</v>
+      </c>
+      <c r="C96" t="s">
+        <v>296</v>
+      </c>
+      <c r="D96" t="s">
+        <v>294</v>
+      </c>
+      <c r="E96" t="s">
         <v>297</v>
-      </c>
-      <c r="C96" t="s">
-        <v>298</v>
-      </c>
-      <c r="D96" t="s">
-        <v>296</v>
-      </c>
-      <c r="E96" t="s">
-        <v>299</v>
       </c>
       <c r="F96" t="s">
         <v>13</v>
@@ -4739,16 +4739,16 @@
         <v>8</v>
       </c>
       <c r="B97" t="s">
+        <v>298</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="D97" t="s">
         <v>300</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="E97" t="s">
         <v>301</v>
-      </c>
-      <c r="D97" t="s">
-        <v>302</v>
-      </c>
-      <c r="E97" t="s">
-        <v>303</v>
       </c>
       <c r="F97" t="s">
         <v>13</v>
@@ -4759,16 +4759,16 @@
         <v>8</v>
       </c>
       <c r="B98" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D98" t="b">
         <v>1</v>
       </c>
       <c r="E98" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F98" t="s">
         <v>13</v>
@@ -4779,16 +4779,16 @@
         <v>8</v>
       </c>
       <c r="B99" t="s">
+        <v>304</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D99" t="s">
+        <v>301</v>
+      </c>
+      <c r="E99" t="s">
         <v>306</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D99" t="s">
-        <v>303</v>
-      </c>
-      <c r="E99" t="s">
-        <v>308</v>
       </c>
       <c r="F99" t="s">
         <v>13</v>
@@ -4799,16 +4799,16 @@
         <v>8</v>
       </c>
       <c r="B100" t="s">
+        <v>307</v>
+      </c>
+      <c r="C100" t="s">
+        <v>308</v>
+      </c>
+      <c r="D100" t="s">
         <v>309</v>
       </c>
-      <c r="C100" t="s">
+      <c r="E100" t="s">
         <v>310</v>
-      </c>
-      <c r="D100" t="s">
-        <v>311</v>
-      </c>
-      <c r="E100" t="s">
-        <v>312</v>
       </c>
       <c r="F100" t="s">
         <v>13</v>
@@ -4819,16 +4819,16 @@
         <v>8</v>
       </c>
       <c r="B101" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C101" t="s">
+        <v>308</v>
+      </c>
+      <c r="D101" t="s">
+        <v>312</v>
+      </c>
+      <c r="E101" t="s">
         <v>310</v>
-      </c>
-      <c r="D101" t="s">
-        <v>314</v>
-      </c>
-      <c r="E101" t="s">
-        <v>312</v>
       </c>
       <c r="F101" t="s">
         <v>13</v>
@@ -4839,16 +4839,16 @@
         <v>8</v>
       </c>
       <c r="B102" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C102" t="s">
+        <v>308</v>
+      </c>
+      <c r="D102" t="s">
+        <v>314</v>
+      </c>
+      <c r="E102" t="s">
         <v>310</v>
-      </c>
-      <c r="D102" t="s">
-        <v>316</v>
-      </c>
-      <c r="E102" t="s">
-        <v>312</v>
       </c>
       <c r="F102" t="s">
         <v>13</v>
@@ -4859,16 +4859,16 @@
         <v>8</v>
       </c>
       <c r="B103" t="s">
+        <v>315</v>
+      </c>
+      <c r="C103" t="s">
+        <v>308</v>
+      </c>
+      <c r="D103" t="s">
+        <v>316</v>
+      </c>
+      <c r="E103" t="s">
         <v>317</v>
-      </c>
-      <c r="C103" t="s">
-        <v>310</v>
-      </c>
-      <c r="D103" t="s">
-        <v>318</v>
-      </c>
-      <c r="E103" t="s">
-        <v>319</v>
       </c>
       <c r="F103" t="s">
         <v>13</v>
@@ -4879,16 +4879,16 @@
         <v>8</v>
       </c>
       <c r="B104" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C104" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D104" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E104" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F104" t="s">
         <v>13</v>
@@ -4899,16 +4899,16 @@
         <v>8</v>
       </c>
       <c r="B105" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C105" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D105" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E105" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F105" t="s">
         <v>13</v>
@@ -4919,16 +4919,16 @@
         <v>8</v>
       </c>
       <c r="B106" t="s">
+        <v>323</v>
+      </c>
+      <c r="C106" t="s">
+        <v>324</v>
+      </c>
+      <c r="D106" t="s">
+        <v>322</v>
+      </c>
+      <c r="E106" t="s">
         <v>325</v>
-      </c>
-      <c r="C106" t="s">
-        <v>326</v>
-      </c>
-      <c r="D106" t="s">
-        <v>324</v>
-      </c>
-      <c r="E106" t="s">
-        <v>327</v>
       </c>
       <c r="F106" t="s">
         <v>13</v>
@@ -4939,16 +4939,16 @@
         <v>8</v>
       </c>
       <c r="B107" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C107" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D107" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E107" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F107" t="s">
         <v>13</v>
@@ -4959,16 +4959,16 @@
         <v>8</v>
       </c>
       <c r="B108" t="s">
+        <v>328</v>
+      </c>
+      <c r="C108" t="s">
+        <v>329</v>
+      </c>
+      <c r="D108" t="b">
+        <v>1</v>
+      </c>
+      <c r="E108" t="s">
         <v>330</v>
-      </c>
-      <c r="C108" t="s">
-        <v>331</v>
-      </c>
-      <c r="D108" t="b">
-        <v>1</v>
-      </c>
-      <c r="E108" t="s">
-        <v>332</v>
       </c>
       <c r="F108" t="s">
         <v>13</v>
@@ -4979,16 +4979,16 @@
         <v>8</v>
       </c>
       <c r="B109" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C109" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D109" t="b">
         <v>1</v>
       </c>
       <c r="E109" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F109" t="s">
         <v>13</v>
@@ -4999,19 +4999,19 @@
         <v>8</v>
       </c>
       <c r="B110" t="s">
+        <v>333</v>
+      </c>
+      <c r="C110" t="s">
+        <v>334</v>
+      </c>
+      <c r="D110" t="s">
         <v>335</v>
       </c>
-      <c r="C110" t="s">
+      <c r="E110" t="s">
         <v>336</v>
       </c>
-      <c r="D110" t="s">
-        <v>337</v>
-      </c>
-      <c r="E110" t="s">
-        <v>338</v>
-      </c>
       <c r="F110" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -5019,19 +5019,19 @@
         <v>8</v>
       </c>
       <c r="B111" t="s">
+        <v>337</v>
+      </c>
+      <c r="C111" t="s">
+        <v>338</v>
+      </c>
+      <c r="D111" t="s">
+        <v>335</v>
+      </c>
+      <c r="E111" t="s">
         <v>339</v>
       </c>
-      <c r="C111" t="s">
-        <v>340</v>
-      </c>
-      <c r="D111" t="s">
-        <v>337</v>
-      </c>
-      <c r="E111" t="s">
-        <v>341</v>
-      </c>
       <c r="F111" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -5039,19 +5039,19 @@
         <v>8</v>
       </c>
       <c r="B112" t="s">
+        <v>340</v>
+      </c>
+      <c r="C112" t="s">
+        <v>341</v>
+      </c>
+      <c r="D112" t="s">
+        <v>335</v>
+      </c>
+      <c r="E112" t="s">
         <v>342</v>
       </c>
-      <c r="C112" t="s">
-        <v>343</v>
-      </c>
-      <c r="D112" t="s">
-        <v>337</v>
-      </c>
-      <c r="E112" t="s">
-        <v>344</v>
-      </c>
       <c r="F112" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -5059,16 +5059,16 @@
         <v>8</v>
       </c>
       <c r="B113" t="s">
+        <v>343</v>
+      </c>
+      <c r="C113" t="s">
+        <v>344</v>
+      </c>
+      <c r="D113" t="s">
         <v>345</v>
       </c>
-      <c r="C113" t="s">
+      <c r="E113" t="s">
         <v>346</v>
-      </c>
-      <c r="D113" t="s">
-        <v>347</v>
-      </c>
-      <c r="E113" t="s">
-        <v>348</v>
       </c>
       <c r="F113" t="s">
         <v>13</v>
@@ -5079,16 +5079,16 @@
         <v>8</v>
       </c>
       <c r="B114" t="s">
+        <v>347</v>
+      </c>
+      <c r="C114" t="s">
+        <v>348</v>
+      </c>
+      <c r="D114" t="s">
         <v>349</v>
       </c>
-      <c r="C114" t="s">
+      <c r="E114" t="s">
         <v>350</v>
-      </c>
-      <c r="D114" t="s">
-        <v>351</v>
-      </c>
-      <c r="E114" t="s">
-        <v>352</v>
       </c>
       <c r="F114" t="s">
         <v>13</v>
@@ -5099,16 +5099,16 @@
         <v>8</v>
       </c>
       <c r="B115" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C115" t="s">
+        <v>348</v>
+      </c>
+      <c r="D115" t="s">
+        <v>352</v>
+      </c>
+      <c r="E115" t="s">
         <v>350</v>
-      </c>
-      <c r="D115" t="s">
-        <v>354</v>
-      </c>
-      <c r="E115" t="s">
-        <v>352</v>
       </c>
       <c r="F115" t="s">
         <v>13</v>
@@ -5119,16 +5119,16 @@
         <v>8</v>
       </c>
       <c r="B116" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C116" t="s">
+        <v>348</v>
+      </c>
+      <c r="D116" t="s">
+        <v>354</v>
+      </c>
+      <c r="E116" t="s">
         <v>350</v>
-      </c>
-      <c r="D116" t="s">
-        <v>356</v>
-      </c>
-      <c r="E116" t="s">
-        <v>352</v>
       </c>
       <c r="F116" t="s">
         <v>13</v>
@@ -5139,16 +5139,16 @@
         <v>8</v>
       </c>
       <c r="B117" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C117" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D117" t="s">
+        <v>356</v>
+      </c>
+      <c r="E117" t="s">
         <v>358</v>
-      </c>
-      <c r="E117" t="s">
-        <v>360</v>
       </c>
       <c r="F117" t="s">
         <v>13</v>
@@ -5159,16 +5159,16 @@
         <v>8</v>
       </c>
       <c r="B118" t="s">
+        <v>359</v>
+      </c>
+      <c r="C118" t="s">
+        <v>360</v>
+      </c>
+      <c r="D118" t="s">
         <v>361</v>
       </c>
-      <c r="C118" t="s">
+      <c r="E118" t="s">
         <v>362</v>
-      </c>
-      <c r="D118" t="s">
-        <v>363</v>
-      </c>
-      <c r="E118" t="s">
-        <v>364</v>
       </c>
       <c r="F118" t="s">
         <v>13</v>
@@ -5179,16 +5179,16 @@
         <v>8</v>
       </c>
       <c r="B119" t="s">
+        <v>363</v>
+      </c>
+      <c r="C119" t="s">
+        <v>360</v>
+      </c>
+      <c r="D119" t="s">
+        <v>364</v>
+      </c>
+      <c r="E119" t="s">
         <v>365</v>
-      </c>
-      <c r="C119" t="s">
-        <v>362</v>
-      </c>
-      <c r="D119" t="s">
-        <v>366</v>
-      </c>
-      <c r="E119" t="s">
-        <v>367</v>
       </c>
       <c r="F119" t="s">
         <v>13</v>
@@ -5199,16 +5199,16 @@
         <v>8</v>
       </c>
       <c r="B120" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C120" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D120" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E120" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F120" t="s">
         <v>13</v>
@@ -5219,16 +5219,16 @@
         <v>8</v>
       </c>
       <c r="B121" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C121" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D121" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E121" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F121" t="s">
         <v>13</v>
@@ -5239,16 +5239,16 @@
         <v>8</v>
       </c>
       <c r="B122" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C122" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D122" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E122" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F122" t="s">
         <v>13</v>
@@ -5259,16 +5259,16 @@
         <v>8</v>
       </c>
       <c r="B123" t="s">
+        <v>375</v>
+      </c>
+      <c r="C123" t="s">
+        <v>376</v>
+      </c>
+      <c r="D123" t="b">
+        <v>1</v>
+      </c>
+      <c r="E123" t="s">
         <v>377</v>
-      </c>
-      <c r="C123" t="s">
-        <v>378</v>
-      </c>
-      <c r="D123" t="b">
-        <v>1</v>
-      </c>
-      <c r="E123" t="s">
-        <v>379</v>
       </c>
       <c r="F123" t="s">
         <v>13</v>
@@ -5279,16 +5279,16 @@
         <v>8</v>
       </c>
       <c r="B124" t="s">
+        <v>378</v>
+      </c>
+      <c r="C124" t="s">
+        <v>379</v>
+      </c>
+      <c r="D124" t="b">
+        <v>1</v>
+      </c>
+      <c r="E124" t="s">
         <v>380</v>
-      </c>
-      <c r="C124" t="s">
-        <v>381</v>
-      </c>
-      <c r="D124" t="b">
-        <v>1</v>
-      </c>
-      <c r="E124" t="s">
-        <v>382</v>
       </c>
       <c r="F124" t="s">
         <v>13</v>
@@ -5299,16 +5299,16 @@
         <v>8</v>
       </c>
       <c r="B125" t="s">
+        <v>381</v>
+      </c>
+      <c r="C125" t="s">
+        <v>382</v>
+      </c>
+      <c r="D125" t="b">
+        <v>1</v>
+      </c>
+      <c r="E125" t="s">
         <v>383</v>
-      </c>
-      <c r="C125" t="s">
-        <v>384</v>
-      </c>
-      <c r="D125" t="b">
-        <v>1</v>
-      </c>
-      <c r="E125" t="s">
-        <v>385</v>
       </c>
       <c r="F125" t="s">
         <v>13</v>
@@ -5319,16 +5319,16 @@
         <v>8</v>
       </c>
       <c r="B126" t="s">
+        <v>384</v>
+      </c>
+      <c r="C126" t="s">
+        <v>385</v>
+      </c>
+      <c r="D126" t="s">
         <v>386</v>
       </c>
-      <c r="C126" t="s">
+      <c r="E126" t="s">
         <v>387</v>
-      </c>
-      <c r="D126" t="s">
-        <v>388</v>
-      </c>
-      <c r="E126" t="s">
-        <v>389</v>
       </c>
       <c r="F126" t="s">
         <v>13</v>
@@ -5339,16 +5339,16 @@
         <v>8</v>
       </c>
       <c r="B127" t="s">
+        <v>388</v>
+      </c>
+      <c r="C127" t="s">
+        <v>389</v>
+      </c>
+      <c r="D127" t="s">
         <v>390</v>
       </c>
-      <c r="C127" t="s">
+      <c r="E127" t="s">
         <v>391</v>
-      </c>
-      <c r="D127" t="s">
-        <v>392</v>
-      </c>
-      <c r="E127" t="s">
-        <v>393</v>
       </c>
       <c r="F127" t="s">
         <v>13</v>
@@ -5359,16 +5359,16 @@
         <v>8</v>
       </c>
       <c r="B128" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C128" t="s">
+        <v>389</v>
+      </c>
+      <c r="D128" t="s">
+        <v>393</v>
+      </c>
+      <c r="E128" t="s">
         <v>391</v>
-      </c>
-      <c r="D128" t="s">
-        <v>395</v>
-      </c>
-      <c r="E128" t="s">
-        <v>393</v>
       </c>
       <c r="F128" t="s">
         <v>13</v>
@@ -5379,16 +5379,16 @@
         <v>8</v>
       </c>
       <c r="B129" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C129" t="s">
+        <v>389</v>
+      </c>
+      <c r="D129" t="s">
+        <v>395</v>
+      </c>
+      <c r="E129" t="s">
         <v>391</v>
-      </c>
-      <c r="D129" t="s">
-        <v>397</v>
-      </c>
-      <c r="E129" t="s">
-        <v>393</v>
       </c>
       <c r="F129" t="s">
         <v>13</v>
@@ -5399,16 +5399,16 @@
         <v>8</v>
       </c>
       <c r="B130" t="s">
+        <v>396</v>
+      </c>
+      <c r="C130" t="s">
+        <v>397</v>
+      </c>
+      <c r="D130" t="s">
         <v>398</v>
       </c>
-      <c r="C130" t="s">
+      <c r="E130" t="s">
         <v>399</v>
-      </c>
-      <c r="D130" t="s">
-        <v>400</v>
-      </c>
-      <c r="E130" t="s">
-        <v>401</v>
       </c>
       <c r="F130" t="s">
         <v>13</v>
@@ -5419,16 +5419,16 @@
         <v>8</v>
       </c>
       <c r="B131" t="s">
+        <v>400</v>
+      </c>
+      <c r="C131" t="s">
+        <v>401</v>
+      </c>
+      <c r="D131" t="s">
         <v>402</v>
       </c>
-      <c r="C131" t="s">
+      <c r="E131" t="s">
         <v>403</v>
-      </c>
-      <c r="D131" t="s">
-        <v>404</v>
-      </c>
-      <c r="E131" t="s">
-        <v>405</v>
       </c>
       <c r="F131" t="s">
         <v>13</v>
@@ -5439,16 +5439,16 @@
         <v>8</v>
       </c>
       <c r="B132" t="s">
+        <v>404</v>
+      </c>
+      <c r="C132" t="s">
+        <v>405</v>
+      </c>
+      <c r="D132" t="s">
         <v>406</v>
       </c>
-      <c r="C132" t="s">
+      <c r="E132" t="s">
         <v>407</v>
-      </c>
-      <c r="D132" t="s">
-        <v>408</v>
-      </c>
-      <c r="E132" t="s">
-        <v>409</v>
       </c>
       <c r="F132" t="s">
         <v>13</v>
@@ -5459,16 +5459,16 @@
         <v>8</v>
       </c>
       <c r="B133" t="s">
+        <v>408</v>
+      </c>
+      <c r="C133" t="s">
+        <v>409</v>
+      </c>
+      <c r="D133" t="s">
         <v>410</v>
       </c>
-      <c r="C133" t="s">
+      <c r="E133" t="s">
         <v>411</v>
-      </c>
-      <c r="D133" t="s">
-        <v>412</v>
-      </c>
-      <c r="E133" t="s">
-        <v>413</v>
       </c>
       <c r="F133" t="s">
         <v>13</v>
@@ -5479,16 +5479,16 @@
         <v>8</v>
       </c>
       <c r="B134" t="s">
+        <v>412</v>
+      </c>
+      <c r="C134" t="s">
+        <v>413</v>
+      </c>
+      <c r="D134" t="s">
         <v>414</v>
       </c>
-      <c r="C134" t="s">
+      <c r="E134" t="s">
         <v>415</v>
-      </c>
-      <c r="D134" t="s">
-        <v>416</v>
-      </c>
-      <c r="E134" t="s">
-        <v>417</v>
       </c>
       <c r="F134" t="s">
         <v>13</v>
@@ -5499,19 +5499,19 @@
         <v>8</v>
       </c>
       <c r="B135" t="s">
+        <v>416</v>
+      </c>
+      <c r="C135" t="s">
+        <v>417</v>
+      </c>
+      <c r="D135" t="b">
+        <v>1</v>
+      </c>
+      <c r="E135" t="s">
         <v>418</v>
       </c>
-      <c r="C135" t="s">
-        <v>419</v>
-      </c>
-      <c r="D135" t="b">
-        <v>1</v>
-      </c>
-      <c r="E135" t="s">
-        <v>420</v>
-      </c>
       <c r="F135" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -5519,19 +5519,19 @@
         <v>8</v>
       </c>
       <c r="B136" t="s">
+        <v>419</v>
+      </c>
+      <c r="C136" t="s">
+        <v>420</v>
+      </c>
+      <c r="D136" t="b">
+        <v>1</v>
+      </c>
+      <c r="E136" t="s">
         <v>421</v>
       </c>
-      <c r="C136" t="s">
-        <v>422</v>
-      </c>
-      <c r="D136" t="b">
-        <v>1</v>
-      </c>
-      <c r="E136" t="s">
-        <v>423</v>
-      </c>
       <c r="F136" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -5539,19 +5539,19 @@
         <v>8</v>
       </c>
       <c r="B137" t="s">
+        <v>422</v>
+      </c>
+      <c r="C137" t="s">
+        <v>423</v>
+      </c>
+      <c r="D137" t="b">
+        <v>1</v>
+      </c>
+      <c r="E137" t="s">
         <v>424</v>
       </c>
-      <c r="C137" t="s">
-        <v>425</v>
-      </c>
-      <c r="D137" t="b">
-        <v>1</v>
-      </c>
-      <c r="E137" t="s">
-        <v>426</v>
-      </c>
       <c r="F137" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -5559,19 +5559,19 @@
         <v>8</v>
       </c>
       <c r="B138" t="s">
+        <v>425</v>
+      </c>
+      <c r="C138" t="s">
+        <v>426</v>
+      </c>
+      <c r="D138" t="b">
+        <v>1</v>
+      </c>
+      <c r="E138" t="s">
         <v>427</v>
       </c>
-      <c r="C138" t="s">
-        <v>428</v>
-      </c>
-      <c r="D138" t="b">
-        <v>1</v>
-      </c>
-      <c r="E138" t="s">
-        <v>429</v>
-      </c>
       <c r="F138" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -5579,19 +5579,19 @@
         <v>8</v>
       </c>
       <c r="B139" t="s">
+        <v>428</v>
+      </c>
+      <c r="C139" t="s">
+        <v>429</v>
+      </c>
+      <c r="D139" t="b">
+        <v>1</v>
+      </c>
+      <c r="E139" t="s">
         <v>430</v>
       </c>
-      <c r="C139" t="s">
-        <v>431</v>
-      </c>
-      <c r="D139" t="b">
-        <v>1</v>
-      </c>
-      <c r="E139" t="s">
-        <v>432</v>
-      </c>
       <c r="F139" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -5599,19 +5599,19 @@
         <v>8</v>
       </c>
       <c r="B140" t="s">
+        <v>431</v>
+      </c>
+      <c r="C140" t="s">
+        <v>432</v>
+      </c>
+      <c r="D140" t="b">
+        <v>1</v>
+      </c>
+      <c r="E140" t="s">
         <v>433</v>
       </c>
-      <c r="C140" t="s">
-        <v>434</v>
-      </c>
-      <c r="D140" t="b">
-        <v>1</v>
-      </c>
-      <c r="E140" t="s">
-        <v>435</v>
-      </c>
       <c r="F140" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -5619,19 +5619,19 @@
         <v>8</v>
       </c>
       <c r="B141" t="s">
+        <v>434</v>
+      </c>
+      <c r="C141" t="s">
+        <v>435</v>
+      </c>
+      <c r="D141" t="b">
+        <v>1</v>
+      </c>
+      <c r="E141" t="s">
         <v>436</v>
       </c>
-      <c r="C141" t="s">
-        <v>437</v>
-      </c>
-      <c r="D141" t="b">
-        <v>1</v>
-      </c>
-      <c r="E141" t="s">
-        <v>438</v>
-      </c>
       <c r="F141" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -5639,16 +5639,16 @@
         <v>8</v>
       </c>
       <c r="B142" t="s">
+        <v>437</v>
+      </c>
+      <c r="C142" t="s">
+        <v>438</v>
+      </c>
+      <c r="D142" t="b">
+        <v>1</v>
+      </c>
+      <c r="E142" t="s">
         <v>439</v>
-      </c>
-      <c r="C142" t="s">
-        <v>440</v>
-      </c>
-      <c r="D142" t="b">
-        <v>1</v>
-      </c>
-      <c r="E142" t="s">
-        <v>441</v>
       </c>
       <c r="F142" t="s">
         <v>13</v>
@@ -5659,16 +5659,16 @@
         <v>8</v>
       </c>
       <c r="B143" t="s">
+        <v>440</v>
+      </c>
+      <c r="C143" t="s">
+        <v>441</v>
+      </c>
+      <c r="D143" t="b">
+        <v>1</v>
+      </c>
+      <c r="E143" t="s">
         <v>442</v>
-      </c>
-      <c r="C143" t="s">
-        <v>443</v>
-      </c>
-      <c r="D143" t="b">
-        <v>1</v>
-      </c>
-      <c r="E143" t="s">
-        <v>444</v>
       </c>
       <c r="F143" t="s">
         <v>13</v>
@@ -5679,16 +5679,16 @@
         <v>8</v>
       </c>
       <c r="B144" t="s">
+        <v>443</v>
+      </c>
+      <c r="C144" t="s">
+        <v>444</v>
+      </c>
+      <c r="D144" t="b">
+        <v>1</v>
+      </c>
+      <c r="E144" t="s">
         <v>445</v>
-      </c>
-      <c r="C144" t="s">
-        <v>446</v>
-      </c>
-      <c r="D144" t="b">
-        <v>1</v>
-      </c>
-      <c r="E144" t="s">
-        <v>447</v>
       </c>
       <c r="F144" t="s">
         <v>13</v>
@@ -5699,16 +5699,16 @@
         <v>8</v>
       </c>
       <c r="B145" t="s">
+        <v>446</v>
+      </c>
+      <c r="C145" t="s">
+        <v>447</v>
+      </c>
+      <c r="D145" t="b">
+        <v>1</v>
+      </c>
+      <c r="E145" t="s">
         <v>448</v>
-      </c>
-      <c r="C145" t="s">
-        <v>449</v>
-      </c>
-      <c r="D145" t="b">
-        <v>1</v>
-      </c>
-      <c r="E145" t="s">
-        <v>450</v>
       </c>
       <c r="F145" t="s">
         <v>13</v>
@@ -5719,16 +5719,16 @@
         <v>8</v>
       </c>
       <c r="B146" t="s">
+        <v>449</v>
+      </c>
+      <c r="C146" t="s">
+        <v>450</v>
+      </c>
+      <c r="D146" t="b">
+        <v>1</v>
+      </c>
+      <c r="E146" t="s">
         <v>451</v>
-      </c>
-      <c r="C146" t="s">
-        <v>452</v>
-      </c>
-      <c r="D146" t="b">
-        <v>1</v>
-      </c>
-      <c r="E146" t="s">
-        <v>453</v>
       </c>
       <c r="F146" t="s">
         <v>13</v>
@@ -5739,16 +5739,16 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
+        <v>452</v>
+      </c>
+      <c r="C147" t="s">
+        <v>453</v>
+      </c>
+      <c r="D147" t="b">
+        <v>1</v>
+      </c>
+      <c r="E147" t="s">
         <v>454</v>
-      </c>
-      <c r="C147" t="s">
-        <v>455</v>
-      </c>
-      <c r="D147" t="b">
-        <v>1</v>
-      </c>
-      <c r="E147" t="s">
-        <v>456</v>
       </c>
       <c r="F147" t="s">
         <v>13</v>
@@ -5759,16 +5759,16 @@
         <v>8</v>
       </c>
       <c r="B148" t="s">
+        <v>455</v>
+      </c>
+      <c r="C148" t="s">
+        <v>456</v>
+      </c>
+      <c r="D148" t="b">
+        <v>1</v>
+      </c>
+      <c r="E148" t="s">
         <v>457</v>
-      </c>
-      <c r="C148" t="s">
-        <v>458</v>
-      </c>
-      <c r="D148" t="b">
-        <v>1</v>
-      </c>
-      <c r="E148" t="s">
-        <v>459</v>
       </c>
       <c r="F148" t="s">
         <v>13</v>
@@ -5779,16 +5779,16 @@
         <v>8</v>
       </c>
       <c r="B149" t="s">
+        <v>458</v>
+      </c>
+      <c r="C149" t="s">
+        <v>459</v>
+      </c>
+      <c r="D149" t="b">
+        <v>1</v>
+      </c>
+      <c r="E149" t="s">
         <v>460</v>
-      </c>
-      <c r="C149" t="s">
-        <v>461</v>
-      </c>
-      <c r="D149" t="b">
-        <v>1</v>
-      </c>
-      <c r="E149" t="s">
-        <v>462</v>
       </c>
       <c r="F149" t="s">
         <v>13</v>
@@ -5799,16 +5799,16 @@
         <v>8</v>
       </c>
       <c r="B150" t="s">
+        <v>461</v>
+      </c>
+      <c r="C150" t="s">
+        <v>462</v>
+      </c>
+      <c r="D150" t="b">
+        <v>1</v>
+      </c>
+      <c r="E150" t="s">
         <v>463</v>
-      </c>
-      <c r="C150" t="s">
-        <v>464</v>
-      </c>
-      <c r="D150" t="b">
-        <v>1</v>
-      </c>
-      <c r="E150" t="s">
-        <v>465</v>
       </c>
       <c r="F150" t="s">
         <v>13</v>
@@ -5819,16 +5819,16 @@
         <v>8</v>
       </c>
       <c r="B151" t="s">
+        <v>464</v>
+      </c>
+      <c r="C151" t="s">
+        <v>465</v>
+      </c>
+      <c r="D151" t="b">
+        <v>1</v>
+      </c>
+      <c r="E151" t="s">
         <v>466</v>
-      </c>
-      <c r="C151" t="s">
-        <v>467</v>
-      </c>
-      <c r="D151" t="b">
-        <v>1</v>
-      </c>
-      <c r="E151" t="s">
-        <v>468</v>
       </c>
       <c r="F151" t="s">
         <v>13</v>
@@ -5839,16 +5839,16 @@
         <v>8</v>
       </c>
       <c r="B152" t="s">
+        <v>467</v>
+      </c>
+      <c r="C152" t="s">
+        <v>468</v>
+      </c>
+      <c r="D152" t="b">
+        <v>1</v>
+      </c>
+      <c r="E152" t="s">
         <v>469</v>
-      </c>
-      <c r="C152" t="s">
-        <v>470</v>
-      </c>
-      <c r="D152" t="b">
-        <v>1</v>
-      </c>
-      <c r="E152" t="s">
-        <v>471</v>
       </c>
       <c r="F152" t="s">
         <v>13</v>
@@ -5859,16 +5859,16 @@
         <v>8</v>
       </c>
       <c r="B153" t="s">
+        <v>470</v>
+      </c>
+      <c r="C153" t="s">
+        <v>471</v>
+      </c>
+      <c r="D153" t="b">
+        <v>1</v>
+      </c>
+      <c r="E153" t="s">
         <v>472</v>
-      </c>
-      <c r="C153" t="s">
-        <v>473</v>
-      </c>
-      <c r="D153" t="b">
-        <v>1</v>
-      </c>
-      <c r="E153" t="s">
-        <v>474</v>
       </c>
       <c r="F153" t="s">
         <v>13</v>
@@ -5879,16 +5879,16 @@
         <v>8</v>
       </c>
       <c r="B154" t="s">
+        <v>473</v>
+      </c>
+      <c r="C154" t="s">
+        <v>474</v>
+      </c>
+      <c r="D154" t="b">
+        <v>1</v>
+      </c>
+      <c r="E154" t="s">
         <v>475</v>
-      </c>
-      <c r="C154" t="s">
-        <v>476</v>
-      </c>
-      <c r="D154" t="b">
-        <v>1</v>
-      </c>
-      <c r="E154" t="s">
-        <v>477</v>
       </c>
       <c r="F154" t="s">
         <v>13</v>
@@ -5899,16 +5899,16 @@
         <v>8</v>
       </c>
       <c r="B155" t="s">
+        <v>476</v>
+      </c>
+      <c r="C155" t="s">
+        <v>477</v>
+      </c>
+      <c r="D155" t="b">
+        <v>1</v>
+      </c>
+      <c r="E155" t="s">
         <v>478</v>
-      </c>
-      <c r="C155" t="s">
-        <v>479</v>
-      </c>
-      <c r="D155" t="b">
-        <v>1</v>
-      </c>
-      <c r="E155" t="s">
-        <v>480</v>
       </c>
       <c r="F155" t="s">
         <v>13</v>
@@ -5919,16 +5919,16 @@
         <v>8</v>
       </c>
       <c r="B156" t="s">
+        <v>479</v>
+      </c>
+      <c r="C156" t="s">
+        <v>480</v>
+      </c>
+      <c r="D156" t="b">
+        <v>1</v>
+      </c>
+      <c r="E156" t="s">
         <v>481</v>
-      </c>
-      <c r="C156" t="s">
-        <v>482</v>
-      </c>
-      <c r="D156" t="b">
-        <v>1</v>
-      </c>
-      <c r="E156" t="s">
-        <v>483</v>
       </c>
       <c r="F156" t="s">
         <v>13</v>
@@ -5939,16 +5939,16 @@
         <v>8</v>
       </c>
       <c r="B157" t="s">
+        <v>482</v>
+      </c>
+      <c r="C157" t="s">
+        <v>483</v>
+      </c>
+      <c r="D157" t="b">
+        <v>1</v>
+      </c>
+      <c r="E157" t="s">
         <v>484</v>
-      </c>
-      <c r="C157" t="s">
-        <v>485</v>
-      </c>
-      <c r="D157" t="b">
-        <v>1</v>
-      </c>
-      <c r="E157" t="s">
-        <v>486</v>
       </c>
       <c r="F157" t="s">
         <v>13</v>
@@ -5959,16 +5959,16 @@
         <v>8</v>
       </c>
       <c r="B158" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C158" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D158" t="b">
         <v>1</v>
       </c>
       <c r="E158" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F158" t="s">
         <v>13</v>
@@ -5979,16 +5979,16 @@
         <v>8</v>
       </c>
       <c r="B159" t="s">
+        <v>487</v>
+      </c>
+      <c r="C159" t="s">
+        <v>488</v>
+      </c>
+      <c r="D159" t="b">
+        <v>1</v>
+      </c>
+      <c r="E159" t="s">
         <v>489</v>
-      </c>
-      <c r="C159" t="s">
-        <v>490</v>
-      </c>
-      <c r="D159" t="b">
-        <v>1</v>
-      </c>
-      <c r="E159" t="s">
-        <v>491</v>
       </c>
       <c r="F159" t="s">
         <v>13</v>
@@ -5999,16 +5999,16 @@
         <v>8</v>
       </c>
       <c r="B160" t="s">
+        <v>490</v>
+      </c>
+      <c r="C160" t="s">
+        <v>491</v>
+      </c>
+      <c r="D160" t="b">
+        <v>1</v>
+      </c>
+      <c r="E160" t="s">
         <v>492</v>
-      </c>
-      <c r="C160" t="s">
-        <v>493</v>
-      </c>
-      <c r="D160" t="b">
-        <v>1</v>
-      </c>
-      <c r="E160" t="s">
-        <v>494</v>
       </c>
       <c r="F160" t="s">
         <v>13</v>
@@ -6019,16 +6019,16 @@
         <v>8</v>
       </c>
       <c r="B161" t="s">
+        <v>493</v>
+      </c>
+      <c r="C161" t="s">
+        <v>494</v>
+      </c>
+      <c r="D161" t="b">
+        <v>1</v>
+      </c>
+      <c r="E161" t="s">
         <v>495</v>
-      </c>
-      <c r="C161" t="s">
-        <v>496</v>
-      </c>
-      <c r="D161" t="b">
-        <v>1</v>
-      </c>
-      <c r="E161" t="s">
-        <v>497</v>
       </c>
       <c r="F161" t="s">
         <v>13</v>
@@ -6039,16 +6039,16 @@
         <v>8</v>
       </c>
       <c r="B162" t="s">
+        <v>496</v>
+      </c>
+      <c r="C162" t="s">
+        <v>497</v>
+      </c>
+      <c r="D162" t="b">
+        <v>1</v>
+      </c>
+      <c r="E162" t="s">
         <v>498</v>
-      </c>
-      <c r="C162" t="s">
-        <v>499</v>
-      </c>
-      <c r="D162" t="b">
-        <v>1</v>
-      </c>
-      <c r="E162" t="s">
-        <v>500</v>
       </c>
       <c r="F162" t="s">
         <v>13</v>
@@ -6059,16 +6059,16 @@
         <v>8</v>
       </c>
       <c r="B163" t="s">
+        <v>499</v>
+      </c>
+      <c r="C163" t="s">
+        <v>500</v>
+      </c>
+      <c r="D163" t="b">
+        <v>1</v>
+      </c>
+      <c r="E163" t="s">
         <v>501</v>
-      </c>
-      <c r="C163" t="s">
-        <v>502</v>
-      </c>
-      <c r="D163" t="b">
-        <v>1</v>
-      </c>
-      <c r="E163" t="s">
-        <v>503</v>
       </c>
       <c r="F163" t="s">
         <v>13</v>
@@ -6079,16 +6079,16 @@
         <v>8</v>
       </c>
       <c r="B164" t="s">
+        <v>502</v>
+      </c>
+      <c r="C164" t="s">
+        <v>503</v>
+      </c>
+      <c r="D164" t="b">
+        <v>1</v>
+      </c>
+      <c r="E164" t="s">
         <v>504</v>
-      </c>
-      <c r="C164" t="s">
-        <v>505</v>
-      </c>
-      <c r="D164" t="b">
-        <v>1</v>
-      </c>
-      <c r="E164" t="s">
-        <v>506</v>
       </c>
       <c r="F164" t="s">
         <v>13</v>
@@ -6099,16 +6099,16 @@
         <v>8</v>
       </c>
       <c r="B165" t="s">
+        <v>505</v>
+      </c>
+      <c r="C165" t="s">
+        <v>506</v>
+      </c>
+      <c r="D165" t="b">
+        <v>1</v>
+      </c>
+      <c r="E165" t="s">
         <v>507</v>
-      </c>
-      <c r="C165" t="s">
-        <v>508</v>
-      </c>
-      <c r="D165" t="b">
-        <v>1</v>
-      </c>
-      <c r="E165" t="s">
-        <v>509</v>
       </c>
       <c r="F165" t="s">
         <v>13</v>
@@ -6119,16 +6119,16 @@
         <v>8</v>
       </c>
       <c r="B166" t="s">
+        <v>508</v>
+      </c>
+      <c r="C166" t="s">
+        <v>509</v>
+      </c>
+      <c r="D166" t="b">
+        <v>1</v>
+      </c>
+      <c r="E166" t="s">
         <v>510</v>
-      </c>
-      <c r="C166" t="s">
-        <v>511</v>
-      </c>
-      <c r="D166" t="b">
-        <v>1</v>
-      </c>
-      <c r="E166" t="s">
-        <v>512</v>
       </c>
       <c r="F166" t="s">
         <v>13</v>
@@ -6139,16 +6139,16 @@
         <v>8</v>
       </c>
       <c r="B167" t="s">
+        <v>511</v>
+      </c>
+      <c r="C167" t="s">
+        <v>512</v>
+      </c>
+      <c r="D167" t="b">
+        <v>1</v>
+      </c>
+      <c r="E167" t="s">
         <v>513</v>
-      </c>
-      <c r="C167" t="s">
-        <v>514</v>
-      </c>
-      <c r="D167" t="b">
-        <v>1</v>
-      </c>
-      <c r="E167" t="s">
-        <v>515</v>
       </c>
       <c r="F167" t="s">
         <v>13</v>
@@ -6159,16 +6159,16 @@
         <v>8</v>
       </c>
       <c r="B168" t="s">
+        <v>514</v>
+      </c>
+      <c r="C168" t="s">
+        <v>515</v>
+      </c>
+      <c r="D168" t="b">
+        <v>1</v>
+      </c>
+      <c r="E168" t="s">
         <v>516</v>
-      </c>
-      <c r="C168" t="s">
-        <v>517</v>
-      </c>
-      <c r="D168" t="b">
-        <v>1</v>
-      </c>
-      <c r="E168" t="s">
-        <v>518</v>
       </c>
       <c r="F168" t="s">
         <v>13</v>
@@ -6179,16 +6179,16 @@
         <v>8</v>
       </c>
       <c r="B169" t="s">
+        <v>517</v>
+      </c>
+      <c r="C169" t="s">
+        <v>518</v>
+      </c>
+      <c r="D169" t="b">
+        <v>1</v>
+      </c>
+      <c r="E169" t="s">
         <v>519</v>
-      </c>
-      <c r="C169" t="s">
-        <v>520</v>
-      </c>
-      <c r="D169" t="b">
-        <v>1</v>
-      </c>
-      <c r="E169" t="s">
-        <v>521</v>
       </c>
       <c r="F169" t="s">
         <v>13</v>
@@ -6199,16 +6199,16 @@
         <v>8</v>
       </c>
       <c r="B170" t="s">
+        <v>520</v>
+      </c>
+      <c r="C170" t="s">
+        <v>521</v>
+      </c>
+      <c r="D170" t="b">
+        <v>1</v>
+      </c>
+      <c r="E170" t="s">
         <v>522</v>
-      </c>
-      <c r="C170" t="s">
-        <v>523</v>
-      </c>
-      <c r="D170" t="b">
-        <v>1</v>
-      </c>
-      <c r="E170" t="s">
-        <v>524</v>
       </c>
       <c r="F170" t="s">
         <v>13</v>
@@ -6219,16 +6219,16 @@
         <v>8</v>
       </c>
       <c r="B171" t="s">
+        <v>523</v>
+      </c>
+      <c r="C171" t="s">
+        <v>524</v>
+      </c>
+      <c r="D171" t="b">
+        <v>1</v>
+      </c>
+      <c r="E171" t="s">
         <v>525</v>
-      </c>
-      <c r="C171" t="s">
-        <v>526</v>
-      </c>
-      <c r="D171" t="b">
-        <v>1</v>
-      </c>
-      <c r="E171" t="s">
-        <v>527</v>
       </c>
       <c r="F171" t="s">
         <v>13</v>
@@ -6239,16 +6239,16 @@
         <v>8</v>
       </c>
       <c r="B172" t="s">
+        <v>526</v>
+      </c>
+      <c r="C172" t="s">
+        <v>527</v>
+      </c>
+      <c r="D172" t="b">
+        <v>1</v>
+      </c>
+      <c r="E172" t="s">
         <v>528</v>
-      </c>
-      <c r="C172" t="s">
-        <v>529</v>
-      </c>
-      <c r="D172" t="b">
-        <v>1</v>
-      </c>
-      <c r="E172" t="s">
-        <v>530</v>
       </c>
       <c r="F172" t="s">
         <v>13</v>
@@ -6259,16 +6259,16 @@
         <v>8</v>
       </c>
       <c r="B173" t="s">
+        <v>529</v>
+      </c>
+      <c r="C173" t="s">
+        <v>530</v>
+      </c>
+      <c r="D173" t="b">
+        <v>1</v>
+      </c>
+      <c r="E173" t="s">
         <v>531</v>
-      </c>
-      <c r="C173" t="s">
-        <v>532</v>
-      </c>
-      <c r="D173" t="b">
-        <v>1</v>
-      </c>
-      <c r="E173" t="s">
-        <v>533</v>
       </c>
       <c r="F173" t="s">
         <v>13</v>
@@ -6279,16 +6279,16 @@
         <v>8</v>
       </c>
       <c r="B174" t="s">
+        <v>532</v>
+      </c>
+      <c r="C174" t="s">
+        <v>533</v>
+      </c>
+      <c r="D174" t="b">
+        <v>1</v>
+      </c>
+      <c r="E174" t="s">
         <v>534</v>
-      </c>
-      <c r="C174" t="s">
-        <v>535</v>
-      </c>
-      <c r="D174" t="b">
-        <v>1</v>
-      </c>
-      <c r="E174" t="s">
-        <v>536</v>
       </c>
       <c r="F174" t="s">
         <v>13</v>
@@ -6299,16 +6299,16 @@
         <v>8</v>
       </c>
       <c r="B175" t="s">
+        <v>535</v>
+      </c>
+      <c r="C175" t="s">
+        <v>536</v>
+      </c>
+      <c r="D175" t="b">
+        <v>1</v>
+      </c>
+      <c r="E175" t="s">
         <v>537</v>
-      </c>
-      <c r="C175" t="s">
-        <v>538</v>
-      </c>
-      <c r="D175" t="b">
-        <v>1</v>
-      </c>
-      <c r="E175" t="s">
-        <v>539</v>
       </c>
       <c r="F175" t="s">
         <v>13</v>
@@ -6319,16 +6319,16 @@
         <v>8</v>
       </c>
       <c r="B176" t="s">
+        <v>538</v>
+      </c>
+      <c r="C176" t="s">
+        <v>539</v>
+      </c>
+      <c r="D176" t="b">
+        <v>1</v>
+      </c>
+      <c r="E176" t="s">
         <v>540</v>
-      </c>
-      <c r="C176" t="s">
-        <v>541</v>
-      </c>
-      <c r="D176" t="b">
-        <v>1</v>
-      </c>
-      <c r="E176" t="s">
-        <v>542</v>
       </c>
       <c r="F176" t="s">
         <v>13</v>
@@ -6339,16 +6339,16 @@
         <v>8</v>
       </c>
       <c r="B177" t="s">
+        <v>541</v>
+      </c>
+      <c r="C177" t="s">
+        <v>542</v>
+      </c>
+      <c r="D177" t="b">
+        <v>1</v>
+      </c>
+      <c r="E177" t="s">
         <v>543</v>
-      </c>
-      <c r="C177" t="s">
-        <v>544</v>
-      </c>
-      <c r="D177" t="b">
-        <v>1</v>
-      </c>
-      <c r="E177" t="s">
-        <v>545</v>
       </c>
       <c r="F177" t="s">
         <v>13</v>
@@ -6359,16 +6359,16 @@
         <v>8</v>
       </c>
       <c r="B178" t="s">
+        <v>544</v>
+      </c>
+      <c r="C178" t="s">
+        <v>545</v>
+      </c>
+      <c r="D178" t="b">
+        <v>1</v>
+      </c>
+      <c r="E178" t="s">
         <v>546</v>
-      </c>
-      <c r="C178" t="s">
-        <v>547</v>
-      </c>
-      <c r="D178" t="b">
-        <v>1</v>
-      </c>
-      <c r="E178" t="s">
-        <v>548</v>
       </c>
       <c r="F178" t="s">
         <v>13</v>
@@ -6379,16 +6379,16 @@
         <v>8</v>
       </c>
       <c r="B179" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C179" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D179" t="b">
         <v>1</v>
       </c>
       <c r="E179" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="F179" t="s">
         <v>13</v>
@@ -6399,16 +6399,16 @@
         <v>8</v>
       </c>
       <c r="B180" t="s">
+        <v>549</v>
+      </c>
+      <c r="C180" t="s">
+        <v>550</v>
+      </c>
+      <c r="D180" t="b">
+        <v>1</v>
+      </c>
+      <c r="E180" t="s">
         <v>551</v>
-      </c>
-      <c r="C180" t="s">
-        <v>552</v>
-      </c>
-      <c r="D180" t="b">
-        <v>1</v>
-      </c>
-      <c r="E180" t="s">
-        <v>553</v>
       </c>
       <c r="F180" t="s">
         <v>13</v>
@@ -6419,16 +6419,16 @@
         <v>8</v>
       </c>
       <c r="B181" t="s">
+        <v>552</v>
+      </c>
+      <c r="C181" t="s">
+        <v>553</v>
+      </c>
+      <c r="D181" t="b">
+        <v>1</v>
+      </c>
+      <c r="E181" t="s">
         <v>554</v>
-      </c>
-      <c r="C181" t="s">
-        <v>555</v>
-      </c>
-      <c r="D181" t="b">
-        <v>1</v>
-      </c>
-      <c r="E181" t="s">
-        <v>556</v>
       </c>
       <c r="F181" t="s">
         <v>13</v>
@@ -6439,16 +6439,16 @@
         <v>8</v>
       </c>
       <c r="B182" t="s">
+        <v>555</v>
+      </c>
+      <c r="C182" t="s">
+        <v>556</v>
+      </c>
+      <c r="D182" t="b">
+        <v>1</v>
+      </c>
+      <c r="E182" t="s">
         <v>557</v>
-      </c>
-      <c r="C182" t="s">
-        <v>558</v>
-      </c>
-      <c r="D182" t="b">
-        <v>1</v>
-      </c>
-      <c r="E182" t="s">
-        <v>559</v>
       </c>
       <c r="F182" t="s">
         <v>13</v>
@@ -6459,16 +6459,16 @@
         <v>8</v>
       </c>
       <c r="B183" t="s">
+        <v>558</v>
+      </c>
+      <c r="C183" t="s">
+        <v>559</v>
+      </c>
+      <c r="D183" t="b">
+        <v>1</v>
+      </c>
+      <c r="E183" t="s">
         <v>560</v>
-      </c>
-      <c r="C183" t="s">
-        <v>561</v>
-      </c>
-      <c r="D183" t="b">
-        <v>1</v>
-      </c>
-      <c r="E183" t="s">
-        <v>562</v>
       </c>
       <c r="F183" t="s">
         <v>13</v>
@@ -6479,16 +6479,16 @@
         <v>8</v>
       </c>
       <c r="B184" t="s">
+        <v>561</v>
+      </c>
+      <c r="C184" t="s">
+        <v>562</v>
+      </c>
+      <c r="D184" t="b">
+        <v>1</v>
+      </c>
+      <c r="E184" t="s">
         <v>563</v>
-      </c>
-      <c r="C184" t="s">
-        <v>564</v>
-      </c>
-      <c r="D184" t="b">
-        <v>1</v>
-      </c>
-      <c r="E184" t="s">
-        <v>565</v>
       </c>
       <c r="F184" t="s">
         <v>13</v>
@@ -6499,16 +6499,16 @@
         <v>8</v>
       </c>
       <c r="B185" t="s">
+        <v>564</v>
+      </c>
+      <c r="C185" t="s">
+        <v>565</v>
+      </c>
+      <c r="D185" t="b">
+        <v>1</v>
+      </c>
+      <c r="E185" t="s">
         <v>566</v>
-      </c>
-      <c r="C185" t="s">
-        <v>567</v>
-      </c>
-      <c r="D185" t="b">
-        <v>1</v>
-      </c>
-      <c r="E185" t="s">
-        <v>568</v>
       </c>
       <c r="F185" t="s">
         <v>13</v>
@@ -6519,16 +6519,16 @@
         <v>8</v>
       </c>
       <c r="B186" t="s">
+        <v>567</v>
+      </c>
+      <c r="C186" t="s">
+        <v>568</v>
+      </c>
+      <c r="D186" t="b">
+        <v>1</v>
+      </c>
+      <c r="E186" t="s">
         <v>569</v>
-      </c>
-      <c r="C186" t="s">
-        <v>570</v>
-      </c>
-      <c r="D186" t="b">
-        <v>1</v>
-      </c>
-      <c r="E186" t="s">
-        <v>571</v>
       </c>
       <c r="F186" t="s">
         <v>13</v>
@@ -6539,16 +6539,16 @@
         <v>8</v>
       </c>
       <c r="B187" t="s">
+        <v>570</v>
+      </c>
+      <c r="C187" t="s">
+        <v>571</v>
+      </c>
+      <c r="D187" t="b">
+        <v>1</v>
+      </c>
+      <c r="E187" t="s">
         <v>572</v>
-      </c>
-      <c r="C187" t="s">
-        <v>573</v>
-      </c>
-      <c r="D187" t="b">
-        <v>1</v>
-      </c>
-      <c r="E187" t="s">
-        <v>574</v>
       </c>
       <c r="F187" t="s">
         <v>13</v>
@@ -6559,16 +6559,16 @@
         <v>8</v>
       </c>
       <c r="B188" t="s">
+        <v>573</v>
+      </c>
+      <c r="C188" t="s">
+        <v>574</v>
+      </c>
+      <c r="D188" t="b">
+        <v>1</v>
+      </c>
+      <c r="E188" t="s">
         <v>575</v>
-      </c>
-      <c r="C188" t="s">
-        <v>576</v>
-      </c>
-      <c r="D188" t="b">
-        <v>1</v>
-      </c>
-      <c r="E188" t="s">
-        <v>577</v>
       </c>
       <c r="F188" t="s">
         <v>13</v>
@@ -6579,16 +6579,16 @@
         <v>8</v>
       </c>
       <c r="B189" t="s">
+        <v>576</v>
+      </c>
+      <c r="C189" t="s">
+        <v>577</v>
+      </c>
+      <c r="D189" t="b">
+        <v>1</v>
+      </c>
+      <c r="E189" t="s">
         <v>578</v>
-      </c>
-      <c r="C189" t="s">
-        <v>579</v>
-      </c>
-      <c r="D189" t="b">
-        <v>1</v>
-      </c>
-      <c r="E189" t="s">
-        <v>580</v>
       </c>
       <c r="F189" t="s">
         <v>13</v>
@@ -6599,16 +6599,16 @@
         <v>8</v>
       </c>
       <c r="B190" t="s">
+        <v>579</v>
+      </c>
+      <c r="C190" t="s">
+        <v>580</v>
+      </c>
+      <c r="D190" t="b">
+        <v>1</v>
+      </c>
+      <c r="E190" t="s">
         <v>581</v>
-      </c>
-      <c r="C190" t="s">
-        <v>582</v>
-      </c>
-      <c r="D190" t="b">
-        <v>1</v>
-      </c>
-      <c r="E190" t="s">
-        <v>583</v>
       </c>
       <c r="F190" t="s">
         <v>13</v>
@@ -6619,16 +6619,16 @@
         <v>8</v>
       </c>
       <c r="B191" t="s">
+        <v>582</v>
+      </c>
+      <c r="C191" t="s">
+        <v>583</v>
+      </c>
+      <c r="D191" t="b">
+        <v>1</v>
+      </c>
+      <c r="E191" t="s">
         <v>584</v>
-      </c>
-      <c r="C191" t="s">
-        <v>585</v>
-      </c>
-      <c r="D191" t="b">
-        <v>1</v>
-      </c>
-      <c r="E191" t="s">
-        <v>586</v>
       </c>
       <c r="F191" t="s">
         <v>13</v>
@@ -6639,16 +6639,16 @@
         <v>8</v>
       </c>
       <c r="B192" t="s">
+        <v>585</v>
+      </c>
+      <c r="C192" t="s">
+        <v>586</v>
+      </c>
+      <c r="D192" t="b">
+        <v>1</v>
+      </c>
+      <c r="E192" t="s">
         <v>587</v>
-      </c>
-      <c r="C192" t="s">
-        <v>588</v>
-      </c>
-      <c r="D192" t="b">
-        <v>1</v>
-      </c>
-      <c r="E192" t="s">
-        <v>589</v>
       </c>
       <c r="F192" t="s">
         <v>13</v>
@@ -6659,16 +6659,16 @@
         <v>8</v>
       </c>
       <c r="B193" t="s">
+        <v>588</v>
+      </c>
+      <c r="C193" t="s">
+        <v>589</v>
+      </c>
+      <c r="D193" t="b">
+        <v>1</v>
+      </c>
+      <c r="E193" t="s">
         <v>590</v>
-      </c>
-      <c r="C193" t="s">
-        <v>591</v>
-      </c>
-      <c r="D193" t="b">
-        <v>1</v>
-      </c>
-      <c r="E193" t="s">
-        <v>592</v>
       </c>
       <c r="F193" t="s">
         <v>13</v>
@@ -6679,16 +6679,16 @@
         <v>8</v>
       </c>
       <c r="B194" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C194" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D194" t="b">
         <v>1</v>
       </c>
       <c r="E194" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="F194" t="s">
         <v>13</v>
@@ -6699,16 +6699,16 @@
         <v>8</v>
       </c>
       <c r="B195" t="s">
+        <v>593</v>
+      </c>
+      <c r="C195" t="s">
+        <v>594</v>
+      </c>
+      <c r="D195" t="b">
+        <v>1</v>
+      </c>
+      <c r="E195" t="s">
         <v>595</v>
-      </c>
-      <c r="C195" t="s">
-        <v>596</v>
-      </c>
-      <c r="D195" t="b">
-        <v>1</v>
-      </c>
-      <c r="E195" t="s">
-        <v>597</v>
       </c>
       <c r="F195" t="s">
         <v>13</v>
@@ -6719,16 +6719,16 @@
         <v>8</v>
       </c>
       <c r="B196" t="s">
+        <v>596</v>
+      </c>
+      <c r="C196" t="s">
+        <v>597</v>
+      </c>
+      <c r="D196" t="b">
+        <v>1</v>
+      </c>
+      <c r="E196" t="s">
         <v>598</v>
-      </c>
-      <c r="C196" t="s">
-        <v>599</v>
-      </c>
-      <c r="D196" t="b">
-        <v>1</v>
-      </c>
-      <c r="E196" t="s">
-        <v>600</v>
       </c>
       <c r="F196" t="s">
         <v>13</v>
@@ -6739,16 +6739,16 @@
         <v>8</v>
       </c>
       <c r="B197" t="s">
+        <v>599</v>
+      </c>
+      <c r="C197" t="s">
+        <v>600</v>
+      </c>
+      <c r="D197" t="b">
+        <v>1</v>
+      </c>
+      <c r="E197" t="s">
         <v>601</v>
-      </c>
-      <c r="C197" t="s">
-        <v>602</v>
-      </c>
-      <c r="D197" t="b">
-        <v>1</v>
-      </c>
-      <c r="E197" t="s">
-        <v>603</v>
       </c>
       <c r="F197" t="s">
         <v>13</v>
@@ -6759,16 +6759,16 @@
         <v>8</v>
       </c>
       <c r="B198" t="s">
+        <v>602</v>
+      </c>
+      <c r="C198" t="s">
+        <v>603</v>
+      </c>
+      <c r="D198" t="b">
+        <v>1</v>
+      </c>
+      <c r="E198" t="s">
         <v>604</v>
-      </c>
-      <c r="C198" t="s">
-        <v>605</v>
-      </c>
-      <c r="D198" t="b">
-        <v>1</v>
-      </c>
-      <c r="E198" t="s">
-        <v>606</v>
       </c>
       <c r="F198" t="s">
         <v>13</v>
@@ -6779,16 +6779,16 @@
         <v>8</v>
       </c>
       <c r="B199" t="s">
+        <v>605</v>
+      </c>
+      <c r="C199" t="s">
+        <v>606</v>
+      </c>
+      <c r="D199" t="b">
+        <v>1</v>
+      </c>
+      <c r="E199" t="s">
         <v>607</v>
-      </c>
-      <c r="C199" t="s">
-        <v>608</v>
-      </c>
-      <c r="D199" t="b">
-        <v>1</v>
-      </c>
-      <c r="E199" t="s">
-        <v>609</v>
       </c>
       <c r="F199" t="s">
         <v>13</v>
@@ -6799,16 +6799,16 @@
         <v>8</v>
       </c>
       <c r="B200" t="s">
+        <v>608</v>
+      </c>
+      <c r="C200" t="s">
+        <v>609</v>
+      </c>
+      <c r="D200" t="b">
+        <v>1</v>
+      </c>
+      <c r="E200" t="s">
         <v>610</v>
-      </c>
-      <c r="C200" t="s">
-        <v>611</v>
-      </c>
-      <c r="D200" t="b">
-        <v>1</v>
-      </c>
-      <c r="E200" t="s">
-        <v>612</v>
       </c>
       <c r="F200" t="s">
         <v>13</v>
@@ -6819,16 +6819,16 @@
         <v>8</v>
       </c>
       <c r="B201" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C201" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D201" t="b">
         <v>1</v>
       </c>
       <c r="E201" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="F201" t="s">
         <v>13</v>
@@ -6839,16 +6839,16 @@
         <v>8</v>
       </c>
       <c r="B202" t="s">
+        <v>613</v>
+      </c>
+      <c r="C202" t="s">
+        <v>614</v>
+      </c>
+      <c r="D202" t="b">
+        <v>1</v>
+      </c>
+      <c r="E202" t="s">
         <v>615</v>
-      </c>
-      <c r="C202" t="s">
-        <v>616</v>
-      </c>
-      <c r="D202" t="b">
-        <v>1</v>
-      </c>
-      <c r="E202" t="s">
-        <v>617</v>
       </c>
       <c r="F202" t="s">
         <v>13</v>
@@ -6859,16 +6859,16 @@
         <v>8</v>
       </c>
       <c r="B203" t="s">
+        <v>616</v>
+      </c>
+      <c r="C203" t="s">
+        <v>617</v>
+      </c>
+      <c r="D203" t="b">
+        <v>1</v>
+      </c>
+      <c r="E203" t="s">
         <v>618</v>
-      </c>
-      <c r="C203" t="s">
-        <v>619</v>
-      </c>
-      <c r="D203" t="b">
-        <v>1</v>
-      </c>
-      <c r="E203" t="s">
-        <v>620</v>
       </c>
       <c r="F203" t="s">
         <v>13</v>
@@ -6879,16 +6879,16 @@
         <v>8</v>
       </c>
       <c r="B204" t="s">
+        <v>619</v>
+      </c>
+      <c r="C204" t="s">
+        <v>620</v>
+      </c>
+      <c r="D204" t="b">
+        <v>1</v>
+      </c>
+      <c r="E204" t="s">
         <v>621</v>
-      </c>
-      <c r="C204" t="s">
-        <v>622</v>
-      </c>
-      <c r="D204" t="b">
-        <v>1</v>
-      </c>
-      <c r="E204" t="s">
-        <v>623</v>
       </c>
       <c r="F204" t="s">
         <v>13</v>
@@ -6899,16 +6899,16 @@
         <v>8</v>
       </c>
       <c r="B205" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C205" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D205" t="b">
         <v>1</v>
       </c>
       <c r="E205" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="F205" t="s">
         <v>13</v>
@@ -6919,16 +6919,16 @@
         <v>8</v>
       </c>
       <c r="B206" t="s">
+        <v>624</v>
+      </c>
+      <c r="C206" t="s">
+        <v>625</v>
+      </c>
+      <c r="D206" t="b">
+        <v>1</v>
+      </c>
+      <c r="E206" t="s">
         <v>626</v>
-      </c>
-      <c r="C206" t="s">
-        <v>627</v>
-      </c>
-      <c r="D206" t="b">
-        <v>1</v>
-      </c>
-      <c r="E206" t="s">
-        <v>628</v>
       </c>
       <c r="F206" t="s">
         <v>13</v>
@@ -6939,16 +6939,16 @@
         <v>8</v>
       </c>
       <c r="B207" t="s">
+        <v>627</v>
+      </c>
+      <c r="C207" t="s">
+        <v>628</v>
+      </c>
+      <c r="D207" t="b">
+        <v>1</v>
+      </c>
+      <c r="E207" t="s">
         <v>629</v>
-      </c>
-      <c r="C207" t="s">
-        <v>630</v>
-      </c>
-      <c r="D207" t="b">
-        <v>1</v>
-      </c>
-      <c r="E207" t="s">
-        <v>631</v>
       </c>
       <c r="F207" t="s">
         <v>13</v>
@@ -6959,16 +6959,16 @@
         <v>8</v>
       </c>
       <c r="B208" t="s">
+        <v>630</v>
+      </c>
+      <c r="C208" t="s">
+        <v>631</v>
+      </c>
+      <c r="D208" t="b">
+        <v>1</v>
+      </c>
+      <c r="E208" t="s">
         <v>632</v>
-      </c>
-      <c r="C208" t="s">
-        <v>633</v>
-      </c>
-      <c r="D208" t="b">
-        <v>1</v>
-      </c>
-      <c r="E208" t="s">
-        <v>634</v>
       </c>
       <c r="F208" t="s">
         <v>13</v>
@@ -6979,16 +6979,16 @@
         <v>8</v>
       </c>
       <c r="B209" t="s">
+        <v>633</v>
+      </c>
+      <c r="C209" t="s">
+        <v>634</v>
+      </c>
+      <c r="D209" t="b">
+        <v>1</v>
+      </c>
+      <c r="E209" t="s">
         <v>635</v>
-      </c>
-      <c r="C209" t="s">
-        <v>636</v>
-      </c>
-      <c r="D209" t="b">
-        <v>1</v>
-      </c>
-      <c r="E209" t="s">
-        <v>637</v>
       </c>
       <c r="F209" t="s">
         <v>13</v>
@@ -6999,16 +6999,16 @@
         <v>8</v>
       </c>
       <c r="B210" t="s">
+        <v>636</v>
+      </c>
+      <c r="C210" t="s">
+        <v>637</v>
+      </c>
+      <c r="D210" t="b">
+        <v>1</v>
+      </c>
+      <c r="E210" t="s">
         <v>638</v>
-      </c>
-      <c r="C210" t="s">
-        <v>639</v>
-      </c>
-      <c r="D210" t="b">
-        <v>1</v>
-      </c>
-      <c r="E210" t="s">
-        <v>640</v>
       </c>
       <c r="F210" t="s">
         <v>13</v>
@@ -7019,16 +7019,16 @@
         <v>8</v>
       </c>
       <c r="B211" t="s">
+        <v>639</v>
+      </c>
+      <c r="C211" t="s">
+        <v>640</v>
+      </c>
+      <c r="D211" t="b">
+        <v>1</v>
+      </c>
+      <c r="E211" t="s">
         <v>641</v>
-      </c>
-      <c r="C211" t="s">
-        <v>642</v>
-      </c>
-      <c r="D211" t="b">
-        <v>1</v>
-      </c>
-      <c r="E211" t="s">
-        <v>643</v>
       </c>
       <c r="F211" t="s">
         <v>13</v>
@@ -7039,16 +7039,16 @@
         <v>8</v>
       </c>
       <c r="B212" t="s">
+        <v>642</v>
+      </c>
+      <c r="C212" t="s">
+        <v>643</v>
+      </c>
+      <c r="D212" t="b">
+        <v>1</v>
+      </c>
+      <c r="E212" t="s">
         <v>644</v>
-      </c>
-      <c r="C212" t="s">
-        <v>645</v>
-      </c>
-      <c r="D212" t="b">
-        <v>1</v>
-      </c>
-      <c r="E212" t="s">
-        <v>646</v>
       </c>
       <c r="F212" t="s">
         <v>13</v>
@@ -7059,16 +7059,16 @@
         <v>8</v>
       </c>
       <c r="B213" t="s">
+        <v>645</v>
+      </c>
+      <c r="C213" t="s">
+        <v>646</v>
+      </c>
+      <c r="D213" t="b">
+        <v>1</v>
+      </c>
+      <c r="E213" t="s">
         <v>647</v>
-      </c>
-      <c r="C213" t="s">
-        <v>648</v>
-      </c>
-      <c r="D213" t="b">
-        <v>1</v>
-      </c>
-      <c r="E213" t="s">
-        <v>649</v>
       </c>
       <c r="F213" t="s">
         <v>13</v>
@@ -7079,16 +7079,16 @@
         <v>8</v>
       </c>
       <c r="B214" t="s">
+        <v>648</v>
+      </c>
+      <c r="C214" t="s">
+        <v>649</v>
+      </c>
+      <c r="D214" t="b">
+        <v>1</v>
+      </c>
+      <c r="E214" t="s">
         <v>650</v>
-      </c>
-      <c r="C214" t="s">
-        <v>651</v>
-      </c>
-      <c r="D214" t="b">
-        <v>1</v>
-      </c>
-      <c r="E214" t="s">
-        <v>652</v>
       </c>
       <c r="F214" t="s">
         <v>13</v>
@@ -7099,16 +7099,16 @@
         <v>8</v>
       </c>
       <c r="B215" t="s">
+        <v>651</v>
+      </c>
+      <c r="C215" t="s">
+        <v>652</v>
+      </c>
+      <c r="D215" t="b">
+        <v>1</v>
+      </c>
+      <c r="E215" t="s">
         <v>653</v>
-      </c>
-      <c r="C215" t="s">
-        <v>654</v>
-      </c>
-      <c r="D215" t="b">
-        <v>1</v>
-      </c>
-      <c r="E215" t="s">
-        <v>655</v>
       </c>
       <c r="F215" t="s">
         <v>13</v>
@@ -7119,16 +7119,16 @@
         <v>8</v>
       </c>
       <c r="B216" t="s">
+        <v>654</v>
+      </c>
+      <c r="C216" t="s">
+        <v>655</v>
+      </c>
+      <c r="D216" t="b">
+        <v>1</v>
+      </c>
+      <c r="E216" t="s">
         <v>656</v>
-      </c>
-      <c r="C216" t="s">
-        <v>657</v>
-      </c>
-      <c r="D216" t="b">
-        <v>1</v>
-      </c>
-      <c r="E216" t="s">
-        <v>658</v>
       </c>
       <c r="F216" t="s">
         <v>13</v>
@@ -7139,16 +7139,16 @@
         <v>8</v>
       </c>
       <c r="B217" t="s">
+        <v>657</v>
+      </c>
+      <c r="C217" t="s">
+        <v>658</v>
+      </c>
+      <c r="D217" t="b">
+        <v>1</v>
+      </c>
+      <c r="E217" t="s">
         <v>659</v>
-      </c>
-      <c r="C217" t="s">
-        <v>660</v>
-      </c>
-      <c r="D217" t="b">
-        <v>1</v>
-      </c>
-      <c r="E217" t="s">
-        <v>661</v>
       </c>
       <c r="F217" t="s">
         <v>13</v>
@@ -7159,16 +7159,16 @@
         <v>8</v>
       </c>
       <c r="B218" t="s">
+        <v>660</v>
+      </c>
+      <c r="C218" t="s">
+        <v>661</v>
+      </c>
+      <c r="D218" t="b">
+        <v>1</v>
+      </c>
+      <c r="E218" t="s">
         <v>662</v>
-      </c>
-      <c r="C218" t="s">
-        <v>663</v>
-      </c>
-      <c r="D218" t="b">
-        <v>1</v>
-      </c>
-      <c r="E218" t="s">
-        <v>664</v>
       </c>
       <c r="F218" t="s">
         <v>13</v>
@@ -7179,16 +7179,16 @@
         <v>8</v>
       </c>
       <c r="B219" t="s">
+        <v>663</v>
+      </c>
+      <c r="C219" t="s">
+        <v>664</v>
+      </c>
+      <c r="D219" t="b">
+        <v>1</v>
+      </c>
+      <c r="E219" t="s">
         <v>665</v>
-      </c>
-      <c r="C219" t="s">
-        <v>666</v>
-      </c>
-      <c r="D219" t="b">
-        <v>1</v>
-      </c>
-      <c r="E219" t="s">
-        <v>667</v>
       </c>
       <c r="F219" t="s">
         <v>13</v>
@@ -7199,16 +7199,16 @@
         <v>8</v>
       </c>
       <c r="B220" t="s">
+        <v>666</v>
+      </c>
+      <c r="C220" t="s">
+        <v>667</v>
+      </c>
+      <c r="D220" t="b">
+        <v>1</v>
+      </c>
+      <c r="E220" t="s">
         <v>668</v>
-      </c>
-      <c r="C220" t="s">
-        <v>669</v>
-      </c>
-      <c r="D220" t="b">
-        <v>1</v>
-      </c>
-      <c r="E220" t="s">
-        <v>670</v>
       </c>
       <c r="F220" t="s">
         <v>13</v>
@@ -7219,16 +7219,16 @@
         <v>8</v>
       </c>
       <c r="B221" t="s">
+        <v>669</v>
+      </c>
+      <c r="C221" t="s">
+        <v>670</v>
+      </c>
+      <c r="D221" t="b">
+        <v>1</v>
+      </c>
+      <c r="E221" t="s">
         <v>671</v>
-      </c>
-      <c r="C221" t="s">
-        <v>672</v>
-      </c>
-      <c r="D221" t="b">
-        <v>1</v>
-      </c>
-      <c r="E221" t="s">
-        <v>673</v>
       </c>
       <c r="F221" t="s">
         <v>13</v>
@@ -7239,16 +7239,16 @@
         <v>8</v>
       </c>
       <c r="B222" t="s">
+        <v>672</v>
+      </c>
+      <c r="C222" t="s">
+        <v>673</v>
+      </c>
+      <c r="D222" t="b">
+        <v>1</v>
+      </c>
+      <c r="E222" t="s">
         <v>674</v>
-      </c>
-      <c r="C222" t="s">
-        <v>675</v>
-      </c>
-      <c r="D222" t="b">
-        <v>1</v>
-      </c>
-      <c r="E222" t="s">
-        <v>676</v>
       </c>
       <c r="F222" t="s">
         <v>13</v>
@@ -7259,16 +7259,16 @@
         <v>8</v>
       </c>
       <c r="B223" t="s">
+        <v>675</v>
+      </c>
+      <c r="C223" t="s">
+        <v>676</v>
+      </c>
+      <c r="D223" t="b">
+        <v>1</v>
+      </c>
+      <c r="E223" t="s">
         <v>677</v>
-      </c>
-      <c r="C223" t="s">
-        <v>678</v>
-      </c>
-      <c r="D223" t="b">
-        <v>1</v>
-      </c>
-      <c r="E223" t="s">
-        <v>679</v>
       </c>
       <c r="F223" t="s">
         <v>13</v>
@@ -7279,16 +7279,16 @@
         <v>8</v>
       </c>
       <c r="B224" t="s">
+        <v>678</v>
+      </c>
+      <c r="C224" t="s">
+        <v>679</v>
+      </c>
+      <c r="D224" t="b">
+        <v>1</v>
+      </c>
+      <c r="E224" t="s">
         <v>680</v>
-      </c>
-      <c r="C224" t="s">
-        <v>681</v>
-      </c>
-      <c r="D224" t="b">
-        <v>1</v>
-      </c>
-      <c r="E224" t="s">
-        <v>682</v>
       </c>
       <c r="F224" t="s">
         <v>13</v>
@@ -7299,16 +7299,16 @@
         <v>8</v>
       </c>
       <c r="B225" t="s">
+        <v>681</v>
+      </c>
+      <c r="C225" t="s">
+        <v>682</v>
+      </c>
+      <c r="D225" t="b">
+        <v>1</v>
+      </c>
+      <c r="E225" t="s">
         <v>683</v>
-      </c>
-      <c r="C225" t="s">
-        <v>684</v>
-      </c>
-      <c r="D225" t="b">
-        <v>1</v>
-      </c>
-      <c r="E225" t="s">
-        <v>685</v>
       </c>
       <c r="F225" t="s">
         <v>13</v>
@@ -7319,16 +7319,16 @@
         <v>8</v>
       </c>
       <c r="B226" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C226" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D226" t="b">
         <v>1</v>
       </c>
       <c r="E226" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="F226" t="s">
         <v>13</v>
@@ -7339,16 +7339,16 @@
         <v>8</v>
       </c>
       <c r="B227" t="s">
+        <v>686</v>
+      </c>
+      <c r="C227" t="s">
+        <v>687</v>
+      </c>
+      <c r="D227" t="b">
+        <v>1</v>
+      </c>
+      <c r="E227" t="s">
         <v>688</v>
-      </c>
-      <c r="C227" t="s">
-        <v>689</v>
-      </c>
-      <c r="D227" t="b">
-        <v>1</v>
-      </c>
-      <c r="E227" t="s">
-        <v>690</v>
       </c>
       <c r="F227" t="s">
         <v>13</v>
@@ -7359,16 +7359,16 @@
         <v>8</v>
       </c>
       <c r="B228" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C228" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D228" t="b">
         <v>1</v>
       </c>
       <c r="E228" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="F228" t="s">
         <v>13</v>
@@ -7379,16 +7379,16 @@
         <v>8</v>
       </c>
       <c r="B229" t="s">
+        <v>691</v>
+      </c>
+      <c r="C229" t="s">
+        <v>692</v>
+      </c>
+      <c r="D229" t="b">
+        <v>1</v>
+      </c>
+      <c r="E229" t="s">
         <v>693</v>
-      </c>
-      <c r="C229" t="s">
-        <v>694</v>
-      </c>
-      <c r="D229" t="b">
-        <v>1</v>
-      </c>
-      <c r="E229" t="s">
-        <v>695</v>
       </c>
       <c r="F229" t="s">
         <v>13</v>
@@ -7399,16 +7399,16 @@
         <v>8</v>
       </c>
       <c r="B230" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C230" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D230" t="b">
         <v>1</v>
       </c>
       <c r="E230" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="F230" t="s">
         <v>13</v>
@@ -7419,16 +7419,16 @@
         <v>8</v>
       </c>
       <c r="B231" t="s">
+        <v>696</v>
+      </c>
+      <c r="C231" t="s">
+        <v>697</v>
+      </c>
+      <c r="D231" t="b">
+        <v>1</v>
+      </c>
+      <c r="E231" t="s">
         <v>698</v>
-      </c>
-      <c r="C231" t="s">
-        <v>699</v>
-      </c>
-      <c r="D231" t="b">
-        <v>1</v>
-      </c>
-      <c r="E231" t="s">
-        <v>700</v>
       </c>
       <c r="F231" t="s">
         <v>13</v>
@@ -7439,16 +7439,16 @@
         <v>8</v>
       </c>
       <c r="B232" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C232" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D232" t="b">
         <v>1</v>
       </c>
       <c r="E232" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="F232" t="s">
         <v>13</v>
@@ -7459,16 +7459,16 @@
         <v>8</v>
       </c>
       <c r="B233" t="s">
+        <v>701</v>
+      </c>
+      <c r="C233" t="s">
+        <v>702</v>
+      </c>
+      <c r="D233" t="b">
+        <v>1</v>
+      </c>
+      <c r="E233" t="s">
         <v>703</v>
-      </c>
-      <c r="C233" t="s">
-        <v>704</v>
-      </c>
-      <c r="D233" t="b">
-        <v>1</v>
-      </c>
-      <c r="E233" t="s">
-        <v>705</v>
       </c>
       <c r="F233" t="s">
         <v>13</v>
@@ -7479,16 +7479,16 @@
         <v>8</v>
       </c>
       <c r="B234" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C234" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D234" t="b">
         <v>1</v>
       </c>
       <c r="E234" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="F234" t="s">
         <v>13</v>
@@ -7499,16 +7499,16 @@
         <v>8</v>
       </c>
       <c r="B235" t="s">
+        <v>706</v>
+      </c>
+      <c r="C235" t="s">
+        <v>707</v>
+      </c>
+      <c r="D235" t="b">
+        <v>1</v>
+      </c>
+      <c r="E235" t="s">
         <v>708</v>
-      </c>
-      <c r="C235" t="s">
-        <v>709</v>
-      </c>
-      <c r="D235" t="b">
-        <v>1</v>
-      </c>
-      <c r="E235" t="s">
-        <v>710</v>
       </c>
       <c r="F235" t="s">
         <v>13</v>
@@ -7519,16 +7519,16 @@
         <v>8</v>
       </c>
       <c r="B236" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C236" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D236" t="b">
         <v>1</v>
       </c>
       <c r="E236" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="F236" t="s">
         <v>13</v>
@@ -7539,16 +7539,16 @@
         <v>8</v>
       </c>
       <c r="B237" t="s">
+        <v>711</v>
+      </c>
+      <c r="C237" t="s">
+        <v>712</v>
+      </c>
+      <c r="D237" t="b">
+        <v>1</v>
+      </c>
+      <c r="E237" t="s">
         <v>713</v>
-      </c>
-      <c r="C237" t="s">
-        <v>714</v>
-      </c>
-      <c r="D237" t="b">
-        <v>1</v>
-      </c>
-      <c r="E237" t="s">
-        <v>715</v>
       </c>
       <c r="F237" t="s">
         <v>13</v>
@@ -7559,16 +7559,16 @@
         <v>8</v>
       </c>
       <c r="B238" t="s">
+        <v>714</v>
+      </c>
+      <c r="C238" t="s">
+        <v>715</v>
+      </c>
+      <c r="D238" t="b">
+        <v>1</v>
+      </c>
+      <c r="E238" t="s">
         <v>716</v>
-      </c>
-      <c r="C238" t="s">
-        <v>717</v>
-      </c>
-      <c r="D238" t="b">
-        <v>1</v>
-      </c>
-      <c r="E238" t="s">
-        <v>718</v>
       </c>
       <c r="F238" t="s">
         <v>13</v>
@@ -7579,16 +7579,16 @@
         <v>8</v>
       </c>
       <c r="B239" t="s">
+        <v>717</v>
+      </c>
+      <c r="C239" t="s">
+        <v>718</v>
+      </c>
+      <c r="D239" t="b">
+        <v>1</v>
+      </c>
+      <c r="E239" t="s">
         <v>719</v>
-      </c>
-      <c r="C239" t="s">
-        <v>720</v>
-      </c>
-      <c r="D239" t="b">
-        <v>1</v>
-      </c>
-      <c r="E239" t="s">
-        <v>721</v>
       </c>
       <c r="F239" t="s">
         <v>13</v>
@@ -7599,16 +7599,16 @@
         <v>8</v>
       </c>
       <c r="B240" t="s">
+        <v>720</v>
+      </c>
+      <c r="C240" t="s">
+        <v>721</v>
+      </c>
+      <c r="D240" t="b">
+        <v>1</v>
+      </c>
+      <c r="E240" t="s">
         <v>722</v>
-      </c>
-      <c r="C240" t="s">
-        <v>723</v>
-      </c>
-      <c r="D240" t="b">
-        <v>1</v>
-      </c>
-      <c r="E240" t="s">
-        <v>724</v>
       </c>
       <c r="F240" t="s">
         <v>13</v>
@@ -7619,16 +7619,16 @@
         <v>8</v>
       </c>
       <c r="B241" t="s">
+        <v>723</v>
+      </c>
+      <c r="C241" t="s">
+        <v>724</v>
+      </c>
+      <c r="D241" t="b">
+        <v>1</v>
+      </c>
+      <c r="E241" t="s">
         <v>725</v>
-      </c>
-      <c r="C241" t="s">
-        <v>726</v>
-      </c>
-      <c r="D241" t="b">
-        <v>1</v>
-      </c>
-      <c r="E241" t="s">
-        <v>727</v>
       </c>
       <c r="F241" t="s">
         <v>13</v>
@@ -7639,16 +7639,16 @@
         <v>8</v>
       </c>
       <c r="B242" t="s">
+        <v>726</v>
+      </c>
+      <c r="C242" t="s">
+        <v>727</v>
+      </c>
+      <c r="D242" t="b">
+        <v>1</v>
+      </c>
+      <c r="E242" t="s">
         <v>728</v>
-      </c>
-      <c r="C242" t="s">
-        <v>729</v>
-      </c>
-      <c r="D242" t="b">
-        <v>1</v>
-      </c>
-      <c r="E242" t="s">
-        <v>730</v>
       </c>
       <c r="F242" t="s">
         <v>13</v>
@@ -7659,16 +7659,16 @@
         <v>8</v>
       </c>
       <c r="B243" t="s">
+        <v>729</v>
+      </c>
+      <c r="C243" t="s">
+        <v>730</v>
+      </c>
+      <c r="D243" t="b">
+        <v>1</v>
+      </c>
+      <c r="E243" t="s">
         <v>731</v>
-      </c>
-      <c r="C243" t="s">
-        <v>732</v>
-      </c>
-      <c r="D243" t="b">
-        <v>1</v>
-      </c>
-      <c r="E243" t="s">
-        <v>733</v>
       </c>
       <c r="F243" t="s">
         <v>13</v>
@@ -7679,16 +7679,16 @@
         <v>8</v>
       </c>
       <c r="B244" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C244" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D244" t="b">
         <v>1</v>
       </c>
       <c r="E244" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="F244" t="s">
         <v>13</v>
@@ -7699,16 +7699,16 @@
         <v>8</v>
       </c>
       <c r="B245" t="s">
+        <v>734</v>
+      </c>
+      <c r="C245" t="s">
+        <v>735</v>
+      </c>
+      <c r="D245" t="b">
+        <v>1</v>
+      </c>
+      <c r="E245" t="s">
         <v>736</v>
-      </c>
-      <c r="C245" t="s">
-        <v>737</v>
-      </c>
-      <c r="D245" t="b">
-        <v>1</v>
-      </c>
-      <c r="E245" t="s">
-        <v>738</v>
       </c>
       <c r="F245" t="s">
         <v>13</v>
@@ -7719,16 +7719,16 @@
         <v>8</v>
       </c>
       <c r="B246" t="s">
+        <v>737</v>
+      </c>
+      <c r="C246" t="s">
+        <v>738</v>
+      </c>
+      <c r="D246" t="b">
+        <v>1</v>
+      </c>
+      <c r="E246" t="s">
         <v>739</v>
-      </c>
-      <c r="C246" t="s">
-        <v>740</v>
-      </c>
-      <c r="D246" t="b">
-        <v>1</v>
-      </c>
-      <c r="E246" t="s">
-        <v>741</v>
       </c>
       <c r="F246" t="s">
         <v>13</v>
@@ -7739,16 +7739,16 @@
         <v>8</v>
       </c>
       <c r="B247" t="s">
+        <v>740</v>
+      </c>
+      <c r="C247" t="s">
+        <v>741</v>
+      </c>
+      <c r="D247" t="b">
+        <v>1</v>
+      </c>
+      <c r="E247" t="s">
         <v>742</v>
-      </c>
-      <c r="C247" t="s">
-        <v>743</v>
-      </c>
-      <c r="D247" t="b">
-        <v>1</v>
-      </c>
-      <c r="E247" t="s">
-        <v>744</v>
       </c>
       <c r="F247" t="s">
         <v>13</v>
@@ -7759,16 +7759,16 @@
         <v>8</v>
       </c>
       <c r="B248" t="s">
+        <v>743</v>
+      </c>
+      <c r="C248" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="D248" t="b">
+        <v>1</v>
+      </c>
+      <c r="E248" s="3" t="s">
         <v>745</v>
-      </c>
-      <c r="C248" s="3" t="s">
-        <v>746</v>
-      </c>
-      <c r="D248" t="b">
-        <v>1</v>
-      </c>
-      <c r="E248" s="3" t="s">
-        <v>747</v>
       </c>
       <c r="F248" t="s">
         <v>13</v>
@@ -7779,16 +7779,16 @@
         <v>8</v>
       </c>
       <c r="B249" t="s">
+        <v>746</v>
+      </c>
+      <c r="C249" s="3" t="s">
+        <v>747</v>
+      </c>
+      <c r="D249" t="b">
+        <v>1</v>
+      </c>
+      <c r="E249" s="3" t="s">
         <v>748</v>
-      </c>
-      <c r="C249" s="3" t="s">
-        <v>749</v>
-      </c>
-      <c r="D249" t="b">
-        <v>1</v>
-      </c>
-      <c r="E249" s="3" t="s">
-        <v>750</v>
       </c>
       <c r="F249" t="s">
         <v>13</v>
@@ -7799,16 +7799,16 @@
         <v>8</v>
       </c>
       <c r="B250" t="s">
+        <v>749</v>
+      </c>
+      <c r="C250" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="D250" t="b">
+        <v>1</v>
+      </c>
+      <c r="E250" s="3" t="s">
         <v>751</v>
-      </c>
-      <c r="C250" s="3" t="s">
-        <v>752</v>
-      </c>
-      <c r="D250" t="b">
-        <v>1</v>
-      </c>
-      <c r="E250" s="3" t="s">
-        <v>753</v>
       </c>
       <c r="F250" t="s">
         <v>13</v>
